--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0E3229-6242-4F11-97D1-1BD7B085ECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFBFE903-5224-45D3-98C9-3159E97341B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,13 +438,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
+    <t>S1aH2,S3aH2,S2aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3</t>
+    <t>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S3aH3,S4aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3</v>
+        <v>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S3aH3,S4aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
+        <v>S1aH2,S3aH2,S2aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048EB620-00CD-4917-8AEF-F3410C79A769}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529697C1-7245-414C-87AE-CCD769B97401}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329F038A-256E-4141-8B39-0A564D089F3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69D70C6-DE77-4A7F-8095-09A6F3393C22}">
   <dimension ref="B9:J190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5689,7 +5689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40223B2-192B-4E4B-AF18-7EE9B76E05FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C9AFD0-4D16-454E-BF5E-A4CC4E7FC748}">
   <dimension ref="B9:BL38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8728,7 +8728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0077F55D-555C-4B47-AAAE-E0423A5A02C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2A2E55-0F80-4B89-ABF8-6971F16B0012}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9287,7 +9287,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.1827333333333333</v>
+        <v>0.18273333333333333</v>
       </c>
       <c r="S22" t="s">
         <v>141</v>
@@ -9919,7 +9919,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.34383333333333327</v>
+        <v>0.34383333333333338</v>
       </c>
       <c r="S62" t="s">
         <v>141</v>
@@ -10591,7 +10591,7 @@
         <v>45</v>
       </c>
       <c r="R110">
-        <v>0.29019999999999996</v>
+        <v>0.29020000000000001</v>
       </c>
       <c r="S110" t="s">
         <v>141</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFBFE903-5224-45D3-98C9-3159E97341B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B36044DD-CA28-46F9-BBD3-6457FB76F7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,13 +438,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S2aH2,S4aH2</t>
+    <t>S2aH2,S3aH2,S1aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S3aH3,S4aH1,S2aH1</t>
+    <t>S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S1aH3,S2aH1,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S1aH1,S4aH3,S3aH1,S2aH3,S3aH3,S4aH1,S2aH1</v>
+        <v>S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S1aH3,S2aH1,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S2aH2,S4aH2</v>
+        <v>S2aH2,S3aH2,S1aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529697C1-7245-414C-87AE-CCD769B97401}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A74EA89-3F76-492E-B430-D88EB0A9A36D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69D70C6-DE77-4A7F-8095-09A6F3393C22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BED8E1D-E41F-44EB-979A-22DBA3CE0DBB}">
   <dimension ref="B9:J190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5689,7 +5689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C9AFD0-4D16-454E-BF5E-A4CC4E7FC748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A673CB5A-C9AE-4F76-92FA-A77F4FBF12C9}">
   <dimension ref="B9:BL38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8728,7 +8728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2A2E55-0F80-4B89-ABF8-6971F16B0012}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C3F6C0-30BD-4430-A6B5-014DFD16491D}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9246,7 +9246,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.16026666666666664</v>
+        <v>0.16026666666666667</v>
       </c>
       <c r="S21" t="s">
         <v>141</v>
@@ -9407,7 +9407,7 @@
         <v>41</v>
       </c>
       <c r="R28">
-        <v>0.42890000000000006</v>
+        <v>0.4289</v>
       </c>
       <c r="S28" t="s">
         <v>141</v>
@@ -9507,7 +9507,7 @@
         <v>43</v>
       </c>
       <c r="R33">
-        <v>0.2699333333333333</v>
+        <v>0.26993333333333336</v>
       </c>
       <c r="S33" t="s">
         <v>141</v>
@@ -9597,7 +9597,7 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.48360000000000003</v>
+        <v>0.48359999999999997</v>
       </c>
       <c r="S39" t="s">
         <v>141</v>
@@ -9877,7 +9877,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.56483333333333341</v>
+        <v>0.5648333333333333</v>
       </c>
       <c r="S59" t="s">
         <v>141</v>
@@ -9891,7 +9891,7 @@
         <v>41</v>
       </c>
       <c r="R60">
-        <v>0.27753333333333335</v>
+        <v>0.2775333333333333</v>
       </c>
       <c r="S60" t="s">
         <v>141</v>
@@ -9961,7 +9961,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.32963333333333328</v>
+        <v>0.32963333333333333</v>
       </c>
       <c r="S65" t="s">
         <v>141</v>
@@ -9989,7 +9989,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.49983333333333335</v>
+        <v>0.4998333333333333</v>
       </c>
       <c r="S67" t="s">
         <v>141</v>
@@ -10129,7 +10129,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.29143333333333327</v>
+        <v>0.29143333333333338</v>
       </c>
       <c r="S77" t="s">
         <v>141</v>
@@ -10157,7 +10157,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.4746333333333333</v>
+        <v>0.47463333333333341</v>
       </c>
       <c r="S79" t="s">
         <v>141</v>
@@ -10213,7 +10213,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.50239999999999996</v>
+        <v>0.50240000000000007</v>
       </c>
       <c r="S83" t="s">
         <v>141</v>
@@ -10353,7 +10353,7 @@
         <v>43</v>
       </c>
       <c r="R93">
-        <v>0.23566666666666666</v>
+        <v>0.23566666666666669</v>
       </c>
       <c r="S93" t="s">
         <v>141</v>
@@ -10409,7 +10409,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.31743333333333329</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="S97" t="s">
         <v>141</v>
@@ -10661,7 +10661,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.54879999999999995</v>
+        <v>0.54880000000000007</v>
       </c>
       <c r="S115" t="s">
         <v>141</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B36044DD-CA28-46F9-BBD3-6457FB76F7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87992945-09F4-467F-8390-4D2B9D7AF252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,13 +438,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S3aH2,S1aH2,S4aH2</t>
+    <t>S4aH2,S3aH2,S2aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S1aH3,S2aH1,S3aH1</t>
+    <t>S3aH1,S2aH1,S1aH1,S4aH3,S3aH3,S4aH1,S2aH3,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S1aH3,S2aH1,S3aH1</v>
+        <v>S3aH1,S2aH1,S1aH1,S4aH3,S3aH3,S4aH1,S2aH3,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S3aH2,S1aH2,S4aH2</v>
+        <v>S4aH2,S3aH2,S2aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A74EA89-3F76-492E-B430-D88EB0A9A36D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9011BA-7D24-456F-AC42-3473F6E6CC1C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BED8E1D-E41F-44EB-979A-22DBA3CE0DBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C006DEB-5E77-4A75-B687-277F5FF5F03E}">
   <dimension ref="B9:J190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5689,7 +5689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A673CB5A-C9AE-4F76-92FA-A77F4FBF12C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72519D5A-3682-4F12-9937-1D8F96B4D546}">
   <dimension ref="B9:BL38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8728,7 +8728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C3F6C0-30BD-4430-A6B5-014DFD16491D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CBB023-0600-4FF3-8610-E41D1B7CF3E9}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8918,7 +8918,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.17110000000000003</v>
+        <v>0.1711</v>
       </c>
       <c r="S13" t="s">
         <v>141</v>
@@ -9082,7 +9082,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S17" t="s">
         <v>141</v>
@@ -9447,7 +9447,7 @@
         <v>45</v>
       </c>
       <c r="R30">
-        <v>0.28333333333333327</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="S30" t="s">
         <v>141</v>
@@ -9569,7 +9569,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.27506666666666663</v>
+        <v>0.27506666666666668</v>
       </c>
       <c r="S37" t="s">
         <v>141</v>
@@ -9807,7 +9807,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22870000000000001</v>
+        <v>0.22869999999999999</v>
       </c>
       <c r="S54" t="s">
         <v>141</v>
@@ -9919,7 +9919,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.34383333333333338</v>
+        <v>0.34383333333333327</v>
       </c>
       <c r="S62" t="s">
         <v>141</v>
@@ -9961,7 +9961,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.32963333333333333</v>
+        <v>0.32963333333333328</v>
       </c>
       <c r="S65" t="s">
         <v>141</v>
@@ -10129,7 +10129,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.29143333333333338</v>
+        <v>0.29143333333333332</v>
       </c>
       <c r="S77" t="s">
         <v>141</v>
@@ -10185,7 +10185,7 @@
         <v>43</v>
       </c>
       <c r="R81">
-        <v>0.30869999999999997</v>
+        <v>0.30870000000000003</v>
       </c>
       <c r="S81" t="s">
         <v>141</v>
@@ -10409,7 +10409,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="S97" t="s">
         <v>141</v>
@@ -10801,7 +10801,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.21666666666666667</v>
+        <v>0.21666666666666665</v>
       </c>
       <c r="S125" t="s">
         <v>141</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87992945-09F4-467F-8390-4D2B9D7AF252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9260F34A-08C3-4CB1-BE51-A13357F88B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,13 +438,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S3aH2,S2aH2,S1aH2</t>
+    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S2aH1,S1aH1,S4aH3,S3aH3,S4aH1,S2aH3,S1aH3</t>
+    <t>S1aH3,S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S2aH1,S1aH1,S4aH3,S3aH3,S4aH1,S2aH3,S1aH3</v>
+        <v>S1aH3,S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S3aH2,S2aH2,S1aH2</v>
+        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9011BA-7D24-456F-AC42-3473F6E6CC1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189425CF-4165-4619-8B0C-A90677A683DF}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C006DEB-5E77-4A75-B687-277F5FF5F03E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B82B697-4862-454C-A8E1-43EFF932F4E1}">
   <dimension ref="B9:J190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5689,7 +5689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72519D5A-3682-4F12-9937-1D8F96B4D546}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3EE0A5-1913-489C-BD5F-0DFCF4144ED3}">
   <dimension ref="B9:BL38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8728,7 +8728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CBB023-0600-4FF3-8610-E41D1B7CF3E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE12BB-D8DE-4852-985E-C295840B5444}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9407,7 +9407,7 @@
         <v>41</v>
       </c>
       <c r="R28">
-        <v>0.4289</v>
+        <v>0.42890000000000006</v>
       </c>
       <c r="S28" t="s">
         <v>141</v>
@@ -9447,7 +9447,7 @@
         <v>45</v>
       </c>
       <c r="R30">
-        <v>0.28333333333333333</v>
+        <v>0.28333333333333327</v>
       </c>
       <c r="S30" t="s">
         <v>141</v>
@@ -9597,7 +9597,7 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.48359999999999997</v>
+        <v>0.48360000000000003</v>
       </c>
       <c r="S39" t="s">
         <v>141</v>
@@ -9807,7 +9807,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22869999999999999</v>
+        <v>0.22870000000000001</v>
       </c>
       <c r="S54" t="s">
         <v>141</v>
@@ -9877,7 +9877,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.5648333333333333</v>
+        <v>0.56483333333333341</v>
       </c>
       <c r="S59" t="s">
         <v>141</v>
@@ -9891,7 +9891,7 @@
         <v>41</v>
       </c>
       <c r="R60">
-        <v>0.2775333333333333</v>
+        <v>0.27753333333333335</v>
       </c>
       <c r="S60" t="s">
         <v>141</v>
@@ -9919,7 +9919,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.34383333333333327</v>
+        <v>0.34383333333333338</v>
       </c>
       <c r="S62" t="s">
         <v>141</v>
@@ -9989,7 +9989,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.4998333333333333</v>
+        <v>0.49983333333333335</v>
       </c>
       <c r="S67" t="s">
         <v>141</v>
@@ -10157,7 +10157,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.47463333333333341</v>
+        <v>0.4746333333333333</v>
       </c>
       <c r="S79" t="s">
         <v>141</v>
@@ -10213,7 +10213,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.50240000000000007</v>
+        <v>0.50239999999999996</v>
       </c>
       <c r="S83" t="s">
         <v>141</v>
@@ -10661,7 +10661,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.54880000000000007</v>
+        <v>0.54879999999999995</v>
       </c>
       <c r="S115" t="s">
         <v>141</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9260F34A-08C3-4CB1-BE51-A13357F88B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9486C95D-FCEF-4CD6-A7F2-E051CF912519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,13 +438,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
+    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1</t>
+    <t>S2aH1,S1aH1,S4aH3,S1aH3,S2aH3,S3aH1,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1</v>
+        <v>S2aH1,S1aH1,S4aH3,S1aH3,S2aH3,S3aH1,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
+        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189425CF-4165-4619-8B0C-A90677A683DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFE2438-D31A-49B4-BE64-E594AB2D8EC8}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B82B697-4862-454C-A8E1-43EFF932F4E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C9343C-581F-48D5-9F76-1FFB3F120D44}">
   <dimension ref="B9:J190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5689,7 +5689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3EE0A5-1913-489C-BD5F-0DFCF4144ED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890F21C7-EA8B-4C9E-9F8B-B2E90DB4728A}">
   <dimension ref="B9:BL38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8728,7 +8728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE12BB-D8DE-4852-985E-C295840B5444}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC67565-769A-4A63-B370-07B442CC7523}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8918,7 +8918,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.1711</v>
+        <v>0.17110000000000003</v>
       </c>
       <c r="S13" t="s">
         <v>141</v>
@@ -9082,7 +9082,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S17" t="s">
         <v>141</v>
@@ -9407,7 +9407,7 @@
         <v>41</v>
       </c>
       <c r="R28">
-        <v>0.42890000000000006</v>
+        <v>0.4289</v>
       </c>
       <c r="S28" t="s">
         <v>141</v>
@@ -9447,7 +9447,7 @@
         <v>45</v>
       </c>
       <c r="R30">
-        <v>0.28333333333333327</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="S30" t="s">
         <v>141</v>
@@ -9569,7 +9569,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.27506666666666668</v>
+        <v>0.27506666666666663</v>
       </c>
       <c r="S37" t="s">
         <v>141</v>
@@ -9807,7 +9807,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22870000000000001</v>
+        <v>0.22869999999999999</v>
       </c>
       <c r="S54" t="s">
         <v>141</v>
@@ -9891,7 +9891,7 @@
         <v>41</v>
       </c>
       <c r="R60">
-        <v>0.27753333333333335</v>
+        <v>0.2775333333333333</v>
       </c>
       <c r="S60" t="s">
         <v>141</v>
@@ -9919,7 +9919,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.34383333333333338</v>
+        <v>0.34383333333333327</v>
       </c>
       <c r="S62" t="s">
         <v>141</v>
@@ -9961,7 +9961,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.32963333333333328</v>
+        <v>0.32963333333333333</v>
       </c>
       <c r="S65" t="s">
         <v>141</v>
@@ -10129,7 +10129,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.29143333333333332</v>
+        <v>0.29143333333333338</v>
       </c>
       <c r="S77" t="s">
         <v>141</v>
@@ -10185,7 +10185,7 @@
         <v>43</v>
       </c>
       <c r="R81">
-        <v>0.30870000000000003</v>
+        <v>0.30869999999999997</v>
       </c>
       <c r="S81" t="s">
         <v>141</v>
@@ -10409,7 +10409,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.31743333333333335</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="S97" t="s">
         <v>141</v>
@@ -10801,7 +10801,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.21666666666666665</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="S125" t="s">
         <v>141</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9486C95D-FCEF-4CD6-A7F2-E051CF912519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D56CCB6-CAA7-47A8-B9FD-3C7B6DB5441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="165">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -318,6 +318,39 @@
     <t>elc_won_HRV_013</t>
   </si>
   <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_001</t>
   </si>
   <si>
@@ -363,6 +396,39 @@
     <t>distr_solelc_spv_HRV_015</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_011</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_001</t>
   </si>
   <si>
@@ -411,6 +477,9 @@
     <t>distr_won*</t>
   </si>
   <si>
+    <t>distr_wof*</t>
+  </si>
+  <si>
     <t>ELC8H</t>
   </si>
   <si>
@@ -438,13 +507,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
+    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S1aH1,S4aH3,S1aH3,S2aH3,S3aH1,S3aH3,S4aH1</t>
+    <t>S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -947,7 +1016,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -956,19 +1025,19 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.45">
@@ -1039,7 +1108,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S1aH1,S4aH3,S1aH3,S2aH3,S3aH1,S3aH3,S4aH1</v>
+        <v>S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1071,7 +1140,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
+        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1167,7 +1236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFE2438-D31A-49B4-BE64-E594AB2D8EC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4C679C-EBD1-4ED1-ACF7-4EFD7815812B}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1251,11 +1320,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C9343C-581F-48D5-9F76-1FFB3F120D44}">
-  <dimension ref="B9:J190"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22546ECA-1805-4E6F-AF6C-898AEC3DE9E1}">
+  <dimension ref="B9:O190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
         <v>~TFM_DINS-AT</v>
@@ -1264,8 +1333,12 @@
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
         <v>~TFM_DINS-AT</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L9" t="str">
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>~TFM_DINS-AT</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>47</v>
       </c>
@@ -1290,8 +1363,20 @@
       <c r="J10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>51</v>
       </c>
@@ -1316,8 +1401,20 @@
       <c r="J11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L11" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11">
+        <v>9.6430260451275077E-2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>51</v>
       </c>
@@ -1342,8 +1439,20 @@
       <c r="J12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L12" t="s">
+        <v>92</v>
+      </c>
+      <c r="M12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12">
+        <v>0.11316469843727361</v>
+      </c>
+      <c r="O12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>51</v>
       </c>
@@ -1368,8 +1477,20 @@
       <c r="J13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L13" t="s">
+        <v>92</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13">
+        <v>7.0579856583626449E-2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>51</v>
       </c>
@@ -1394,8 +1515,20 @@
       <c r="J14" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L14" t="s">
+        <v>92</v>
+      </c>
+      <c r="M14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14">
+        <v>0.10783367256097975</v>
+      </c>
+      <c r="O14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>51</v>
       </c>
@@ -1420,8 +1553,20 @@
       <c r="J15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L15" t="s">
+        <v>92</v>
+      </c>
+      <c r="M15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15">
+        <v>0.10061661593548224</v>
+      </c>
+      <c r="O15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>51</v>
       </c>
@@ -1446,8 +1591,20 @@
       <c r="J16" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16">
+        <v>7.8201983450920956E-2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>51</v>
       </c>
@@ -1472,8 +1629,20 @@
       <c r="J17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L17" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17">
+        <v>5.8905596496724798E-2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>51</v>
       </c>
@@ -1498,8 +1667,20 @@
       <c r="J18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L18" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18">
+        <v>4.1415161224094395E-2</v>
+      </c>
+      <c r="O18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>51</v>
       </c>
@@ -1524,8 +1705,20 @@
       <c r="J19" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19">
+        <v>3.358829531364517E-2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>51</v>
       </c>
@@ -1550,8 +1743,20 @@
       <c r="J20" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20">
+        <v>0.10280061453101681</v>
+      </c>
+      <c r="O20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>51</v>
       </c>
@@ -1576,8 +1781,20 @@
       <c r="J21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L21" t="s">
+        <v>92</v>
+      </c>
+      <c r="M21" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21">
+        <v>0.11646751342068905</v>
+      </c>
+      <c r="O21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>51</v>
       </c>
@@ -1602,8 +1819,20 @@
       <c r="J22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L22" t="s">
+        <v>92</v>
+      </c>
+      <c r="M22" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22">
+        <v>7.9995731594273117E-2</v>
+      </c>
+      <c r="O22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>65</v>
       </c>
@@ -1628,8 +1857,20 @@
       <c r="J23" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L23" t="s">
+        <v>93</v>
+      </c>
+      <c r="M23" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23">
+        <v>8.788599755368208E-2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>65</v>
       </c>
@@ -1654,8 +1895,20 @@
       <c r="J24" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L24" t="s">
+        <v>93</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24">
+        <v>0.10793002390059721</v>
+      </c>
+      <c r="O24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>65</v>
       </c>
@@ -1680,8 +1933,20 @@
       <c r="J25" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L25" t="s">
+        <v>93</v>
+      </c>
+      <c r="M25" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25">
+        <v>6.6823637590192109E-2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>65</v>
       </c>
@@ -1706,8 +1971,20 @@
       <c r="J26" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L26" t="s">
+        <v>93</v>
+      </c>
+      <c r="M26" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26">
+        <v>9.7242428570273501E-2</v>
+      </c>
+      <c r="O26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>65</v>
       </c>
@@ -1732,8 +2009,20 @@
       <c r="J27" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L27" t="s">
+        <v>93</v>
+      </c>
+      <c r="M27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27">
+        <v>0.10635752870882673</v>
+      </c>
+      <c r="O27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>65</v>
       </c>
@@ -1758,8 +2047,20 @@
       <c r="J28" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L28" t="s">
+        <v>93</v>
+      </c>
+      <c r="M28" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28">
+        <v>8.4941237116718998E-2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>65</v>
       </c>
@@ -1784,8 +2085,20 @@
       <c r="J29" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L29" t="s">
+        <v>93</v>
+      </c>
+      <c r="M29" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29">
+        <v>5.757136853929911E-2</v>
+      </c>
+      <c r="O29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>65</v>
       </c>
@@ -1810,8 +2123,20 @@
       <c r="J30" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L30" t="s">
+        <v>93</v>
+      </c>
+      <c r="M30" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30">
+        <v>7.30206442670263E-2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>65</v>
       </c>
@@ -1836,8 +2161,20 @@
       <c r="J31" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L31" t="s">
+        <v>93</v>
+      </c>
+      <c r="M31" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31">
+        <v>5.9535059331900585E-2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>65</v>
       </c>
@@ -1862,8 +2199,20 @@
       <c r="J32" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L32" t="s">
+        <v>93</v>
+      </c>
+      <c r="M32" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32">
+        <v>8.3773911305654411E-2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>65</v>
       </c>
@@ -1888,8 +2237,20 @@
       <c r="J33" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L33" t="s">
+        <v>93</v>
+      </c>
+      <c r="M33" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33">
+        <v>0.10521838510445096</v>
+      </c>
+      <c r="O33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>65</v>
       </c>
@@ -1914,8 +2275,20 @@
       <c r="J34" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L34" t="s">
+        <v>93</v>
+      </c>
+      <c r="M34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N34">
+        <v>6.9699778011374905E-2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>66</v>
       </c>
@@ -1940,8 +2313,20 @@
       <c r="J35" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L35" t="s">
+        <v>94</v>
+      </c>
+      <c r="M35" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35">
+        <v>9.2661785839646779E-2</v>
+      </c>
+      <c r="O35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>66</v>
       </c>
@@ -1966,8 +2351,20 @@
       <c r="J36" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L36" t="s">
+        <v>94</v>
+      </c>
+      <c r="M36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36">
+        <v>0.11889356647960792</v>
+      </c>
+      <c r="O36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>66</v>
       </c>
@@ -1992,8 +2389,20 @@
       <c r="J37" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L37" t="s">
+        <v>94</v>
+      </c>
+      <c r="M37" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37">
+        <v>7.2843711144560896E-2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>66</v>
       </c>
@@ -2018,8 +2427,20 @@
       <c r="J38" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L38" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38">
+        <v>0.1142313166433786</v>
+      </c>
+      <c r="O38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>66</v>
       </c>
@@ -2044,8 +2465,20 @@
       <c r="J39" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L39" t="s">
+        <v>94</v>
+      </c>
+      <c r="M39" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39">
+        <v>0.11189507127466021</v>
+      </c>
+      <c r="O39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>66</v>
       </c>
@@ -2070,8 +2503,20 @@
       <c r="J40" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L40" t="s">
+        <v>94</v>
+      </c>
+      <c r="M40" t="s">
+        <v>58</v>
+      </c>
+      <c r="N40">
+        <v>8.5249422769694008E-2</v>
+      </c>
+      <c r="O40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>66</v>
       </c>
@@ -2096,8 +2541,20 @@
       <c r="J41" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L41" t="s">
+        <v>94</v>
+      </c>
+      <c r="M41" t="s">
+        <v>59</v>
+      </c>
+      <c r="N41">
+        <v>5.0681825823284912E-2</v>
+      </c>
+      <c r="O41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>66</v>
       </c>
@@ -2122,8 +2579,20 @@
       <c r="J42" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L42" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" t="s">
+        <v>60</v>
+      </c>
+      <c r="N42">
+        <v>5.8592841251774427E-2</v>
+      </c>
+      <c r="O42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>66</v>
       </c>
@@ -2148,8 +2617,20 @@
       <c r="J43" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L43" t="s">
+        <v>94</v>
+      </c>
+      <c r="M43" t="s">
+        <v>61</v>
+      </c>
+      <c r="N43">
+        <v>5.6383663463398584E-2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>66</v>
       </c>
@@ -2174,8 +2655,20 @@
       <c r="J44" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L44" t="s">
+        <v>94</v>
+      </c>
+      <c r="M44" t="s">
+        <v>62</v>
+      </c>
+      <c r="N44">
+        <v>7.6400469021211032E-2</v>
+      </c>
+      <c r="O44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>66</v>
       </c>
@@ -2200,8 +2693,20 @@
       <c r="J45" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L45" t="s">
+        <v>94</v>
+      </c>
+      <c r="M45" t="s">
+        <v>63</v>
+      </c>
+      <c r="N45">
+        <v>9.5632932794347578E-2</v>
+      </c>
+      <c r="O45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>66</v>
       </c>
@@ -2226,8 +2731,20 @@
       <c r="J46" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" t="s">
+        <v>64</v>
+      </c>
+      <c r="N46">
+        <v>6.6533393494435905E-2</v>
+      </c>
+      <c r="O46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>67</v>
       </c>
@@ -2252,8 +2769,20 @@
       <c r="J47" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L47" t="s">
+        <v>95</v>
+      </c>
+      <c r="M47" t="s">
+        <v>52</v>
+      </c>
+      <c r="N47">
+        <v>8.7199104864846749E-2</v>
+      </c>
+      <c r="O47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -2278,8 +2807,20 @@
       <c r="J48" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L48" t="s">
+        <v>95</v>
+      </c>
+      <c r="M48" t="s">
+        <v>54</v>
+      </c>
+      <c r="N48">
+        <v>0.10881850109433965</v>
+      </c>
+      <c r="O48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>67</v>
       </c>
@@ -2304,8 +2845,20 @@
       <c r="J49" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>95</v>
+      </c>
+      <c r="M49" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49">
+        <v>6.5765496823334352E-2</v>
+      </c>
+      <c r="O49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>67</v>
       </c>
@@ -2330,8 +2883,20 @@
       <c r="J50" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>95</v>
+      </c>
+      <c r="M50" t="s">
+        <v>56</v>
+      </c>
+      <c r="N50">
+        <v>0.10313116840068419</v>
+      </c>
+      <c r="O50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>67</v>
       </c>
@@ -2356,8 +2921,20 @@
       <c r="J51" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>95</v>
+      </c>
+      <c r="M51" t="s">
+        <v>57</v>
+      </c>
+      <c r="N51">
+        <v>0.11063654838616771</v>
+      </c>
+      <c r="O51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>67</v>
       </c>
@@ -2382,8 +2959,20 @@
       <c r="J52" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>95</v>
+      </c>
+      <c r="M52" t="s">
+        <v>58</v>
+      </c>
+      <c r="N52">
+        <v>8.5321960101863631E-2</v>
+      </c>
+      <c r="O52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>67</v>
       </c>
@@ -2408,8 +2997,20 @@
       <c r="J53" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>95</v>
+      </c>
+      <c r="M53" t="s">
+        <v>59</v>
+      </c>
+      <c r="N53">
+        <v>5.4711347628539936E-2</v>
+      </c>
+      <c r="O53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>67</v>
       </c>
@@ -2434,8 +3035,20 @@
       <c r="J54" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>95</v>
+      </c>
+      <c r="M54" t="s">
+        <v>60</v>
+      </c>
+      <c r="N54">
+        <v>7.6903066383892271E-2</v>
+      </c>
+      <c r="O54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>67</v>
       </c>
@@ -2460,8 +3073,20 @@
       <c r="J55" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>95</v>
+      </c>
+      <c r="M55" t="s">
+        <v>61</v>
+      </c>
+      <c r="N55">
+        <v>5.664863398821255E-2</v>
+      </c>
+      <c r="O55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>67</v>
       </c>
@@ -2486,8 +3111,20 @@
       <c r="J56" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>95</v>
+      </c>
+      <c r="M56" t="s">
+        <v>62</v>
+      </c>
+      <c r="N56">
+        <v>8.4595183564421805E-2</v>
+      </c>
+      <c r="O56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>67</v>
       </c>
@@ -2512,8 +3149,20 @@
       <c r="J57" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L57" t="s">
+        <v>95</v>
+      </c>
+      <c r="M57" t="s">
+        <v>63</v>
+      </c>
+      <c r="N57">
+        <v>9.9744026299003141E-2</v>
+      </c>
+      <c r="O57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>67</v>
       </c>
@@ -2538,8 +3187,20 @@
       <c r="J58" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L58" t="s">
+        <v>95</v>
+      </c>
+      <c r="M58" t="s">
+        <v>64</v>
+      </c>
+      <c r="N58">
+        <v>6.6524962464694581E-2</v>
+      </c>
+      <c r="O58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>68</v>
       </c>
@@ -2564,8 +3225,20 @@
       <c r="J59" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L59" t="s">
+        <v>96</v>
+      </c>
+      <c r="M59" t="s">
+        <v>52</v>
+      </c>
+      <c r="N59">
+        <v>9.5256649549869954E-2</v>
+      </c>
+      <c r="O59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>68</v>
       </c>
@@ -2590,8 +3263,20 @@
       <c r="J60" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L60" t="s">
+        <v>96</v>
+      </c>
+      <c r="M60" t="s">
+        <v>54</v>
+      </c>
+      <c r="N60">
+        <v>0.11235670757008792</v>
+      </c>
+      <c r="O60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>68</v>
       </c>
@@ -2616,8 +3301,20 @@
       <c r="J61" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L61" t="s">
+        <v>96</v>
+      </c>
+      <c r="M61" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61">
+        <v>7.3837064509453709E-2</v>
+      </c>
+      <c r="O61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>68</v>
       </c>
@@ -2642,8 +3339,20 @@
       <c r="J62" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L62" t="s">
+        <v>96</v>
+      </c>
+      <c r="M62" t="s">
+        <v>56</v>
+      </c>
+      <c r="N62">
+        <v>9.3510818633788712E-2</v>
+      </c>
+      <c r="O62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>68</v>
       </c>
@@ -2668,8 +3377,20 @@
       <c r="J63" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L63" t="s">
+        <v>96</v>
+      </c>
+      <c r="M63" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63">
+        <v>0.11578487020991521</v>
+      </c>
+      <c r="O63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>68</v>
       </c>
@@ -2694,8 +3415,20 @@
       <c r="J64" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L64" t="s">
+        <v>96</v>
+      </c>
+      <c r="M64" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64">
+        <v>7.4666026248330589E-2</v>
+      </c>
+      <c r="O64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>68</v>
       </c>
@@ -2720,8 +3453,20 @@
       <c r="J65" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L65" t="s">
+        <v>96</v>
+      </c>
+      <c r="M65" t="s">
+        <v>59</v>
+      </c>
+      <c r="N65">
+        <v>5.055847210287754E-2</v>
+      </c>
+      <c r="O65" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>68</v>
       </c>
@@ -2746,8 +3491,20 @@
       <c r="J66" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L66" t="s">
+        <v>96</v>
+      </c>
+      <c r="M66" t="s">
+        <v>60</v>
+      </c>
+      <c r="N66">
+        <v>7.0413379904161744E-2</v>
+      </c>
+      <c r="O66" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>68</v>
       </c>
@@ -2772,8 +3529,20 @@
       <c r="J67" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L67" t="s">
+        <v>96</v>
+      </c>
+      <c r="M67" t="s">
+        <v>61</v>
+      </c>
+      <c r="N67">
+        <v>5.5819567306111831E-2</v>
+      </c>
+      <c r="O67" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>68</v>
       </c>
@@ -2798,8 +3567,20 @@
       <c r="J68" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L68" t="s">
+        <v>96</v>
+      </c>
+      <c r="M68" t="s">
+        <v>62</v>
+      </c>
+      <c r="N68">
+        <v>8.4749786980720748E-2</v>
+      </c>
+      <c r="O68" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>68</v>
       </c>
@@ -2824,8 +3605,20 @@
       <c r="J69" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L69" t="s">
+        <v>96</v>
+      </c>
+      <c r="M69" t="s">
+        <v>63</v>
+      </c>
+      <c r="N69">
+        <v>0.10618495801505962</v>
+      </c>
+      <c r="O69" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>68</v>
       </c>
@@ -2850,8 +3643,20 @@
       <c r="J70" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L70" t="s">
+        <v>96</v>
+      </c>
+      <c r="M70" t="s">
+        <v>64</v>
+      </c>
+      <c r="N70">
+        <v>6.6861698969623171E-2</v>
+      </c>
+      <c r="O70" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>69</v>
       </c>
@@ -2876,8 +3681,20 @@
       <c r="J71" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L71" t="s">
+        <v>97</v>
+      </c>
+      <c r="M71" t="s">
+        <v>52</v>
+      </c>
+      <c r="N71">
+        <v>9.5747048585354308E-2</v>
+      </c>
+      <c r="O71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>69</v>
       </c>
@@ -2902,8 +3719,20 @@
       <c r="J72" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L72" t="s">
+        <v>97</v>
+      </c>
+      <c r="M72" t="s">
+        <v>54</v>
+      </c>
+      <c r="N72">
+        <v>0.11150255421483604</v>
+      </c>
+      <c r="O72" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>69</v>
       </c>
@@ -2928,8 +3757,20 @@
       <c r="J73" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L73" t="s">
+        <v>97</v>
+      </c>
+      <c r="M73" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73">
+        <v>7.4840025372917063E-2</v>
+      </c>
+      <c r="O73" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>69</v>
       </c>
@@ -2954,8 +3795,20 @@
       <c r="J74" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L74" t="s">
+        <v>97</v>
+      </c>
+      <c r="M74" t="s">
+        <v>56</v>
+      </c>
+      <c r="N74">
+        <v>9.0901417627186301E-2</v>
+      </c>
+      <c r="O74" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>69</v>
       </c>
@@ -2980,8 +3833,20 @@
       <c r="J75" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L75" t="s">
+        <v>97</v>
+      </c>
+      <c r="M75" t="s">
+        <v>57</v>
+      </c>
+      <c r="N75">
+        <v>0.11256343088516321</v>
+      </c>
+      <c r="O75" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>69</v>
       </c>
@@ -3006,8 +3871,20 @@
       <c r="J76" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L76" t="s">
+        <v>97</v>
+      </c>
+      <c r="M76" t="s">
+        <v>58</v>
+      </c>
+      <c r="N76">
+        <v>7.1773131809560506E-2</v>
+      </c>
+      <c r="O76" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>69</v>
       </c>
@@ -3032,8 +3909,20 @@
       <c r="J77" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L77" t="s">
+        <v>97</v>
+      </c>
+      <c r="M77" t="s">
+        <v>59</v>
+      </c>
+      <c r="N77">
+        <v>4.9182128486274637E-2</v>
+      </c>
+      <c r="O77" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>69</v>
       </c>
@@ -3058,8 +3947,20 @@
       <c r="J78" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L78" t="s">
+        <v>97</v>
+      </c>
+      <c r="M78" t="s">
+        <v>60</v>
+      </c>
+      <c r="N78">
+        <v>7.1211420105843179E-2</v>
+      </c>
+      <c r="O78" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>69</v>
       </c>
@@ -3084,8 +3985,20 @@
       <c r="J79" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L79" t="s">
+        <v>97</v>
+      </c>
+      <c r="M79" t="s">
+        <v>61</v>
+      </c>
+      <c r="N79">
+        <v>5.8150344462939145E-2</v>
+      </c>
+      <c r="O79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>69</v>
       </c>
@@ -3110,8 +4023,20 @@
       <c r="J80" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L80" t="s">
+        <v>97</v>
+      </c>
+      <c r="M80" t="s">
+        <v>62</v>
+      </c>
+      <c r="N80">
+        <v>8.7793306413368924E-2</v>
+      </c>
+      <c r="O80" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>69</v>
       </c>
@@ -3136,8 +4061,20 @@
       <c r="J81" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L81" t="s">
+        <v>97</v>
+      </c>
+      <c r="M81" t="s">
+        <v>63</v>
+      </c>
+      <c r="N81">
+        <v>0.10713766332340308</v>
+      </c>
+      <c r="O81" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>69</v>
       </c>
@@ -3162,8 +4099,20 @@
       <c r="J82" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L82" t="s">
+        <v>97</v>
+      </c>
+      <c r="M82" t="s">
+        <v>64</v>
+      </c>
+      <c r="N82">
+        <v>6.9197528713151865E-2</v>
+      </c>
+      <c r="O82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>70</v>
       </c>
@@ -3188,8 +4137,20 @@
       <c r="J83" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L83" t="s">
+        <v>98</v>
+      </c>
+      <c r="M83" t="s">
+        <v>52</v>
+      </c>
+      <c r="N83">
+        <v>9.2292982317460387E-2</v>
+      </c>
+      <c r="O83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>70</v>
       </c>
@@ -3214,8 +4175,20 @@
       <c r="J84" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L84" t="s">
+        <v>98</v>
+      </c>
+      <c r="M84" t="s">
+        <v>54</v>
+      </c>
+      <c r="N84">
+        <v>0.11725363129950024</v>
+      </c>
+      <c r="O84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>70</v>
       </c>
@@ -3240,8 +4213,20 @@
       <c r="J85" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L85" t="s">
+        <v>98</v>
+      </c>
+      <c r="M85" t="s">
+        <v>55</v>
+      </c>
+      <c r="N85">
+        <v>7.3071301407948611E-2</v>
+      </c>
+      <c r="O85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>70</v>
       </c>
@@ -3266,8 +4251,20 @@
       <c r="J86" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L86" t="s">
+        <v>98</v>
+      </c>
+      <c r="M86" t="s">
+        <v>56</v>
+      </c>
+      <c r="N86">
+        <v>9.6111070227046888E-2</v>
+      </c>
+      <c r="O86" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>70</v>
       </c>
@@ -3292,8 +4289,20 @@
       <c r="J87" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L87" t="s">
+        <v>98</v>
+      </c>
+      <c r="M87" t="s">
+        <v>57</v>
+      </c>
+      <c r="N87">
+        <v>0.11754418651779062</v>
+      </c>
+      <c r="O87" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="88" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>70</v>
       </c>
@@ -3318,8 +4327,20 @@
       <c r="J88" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L88" t="s">
+        <v>98</v>
+      </c>
+      <c r="M88" t="s">
+        <v>58</v>
+      </c>
+      <c r="N88">
+        <v>7.8266724132882506E-2</v>
+      </c>
+      <c r="O88" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>70</v>
       </c>
@@ -3344,8 +4365,20 @@
       <c r="J89" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L89" t="s">
+        <v>98</v>
+      </c>
+      <c r="M89" t="s">
+        <v>59</v>
+      </c>
+      <c r="N89">
+        <v>3.8681704501927185E-2</v>
+      </c>
+      <c r="O89" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
         <v>70</v>
       </c>
@@ -3370,8 +4403,20 @@
       <c r="J90" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L90" t="s">
+        <v>98</v>
+      </c>
+      <c r="M90" t="s">
+        <v>60</v>
+      </c>
+      <c r="N90">
+        <v>5.6044314663537168E-2</v>
+      </c>
+      <c r="O90" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="91" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>70</v>
       </c>
@@ -3396,8 +4441,20 @@
       <c r="J91" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L91" t="s">
+        <v>98</v>
+      </c>
+      <c r="M91" t="s">
+        <v>61</v>
+      </c>
+      <c r="N91">
+        <v>5.0260477211982429E-2</v>
+      </c>
+      <c r="O91" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="92" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
         <v>70</v>
       </c>
@@ -3422,8 +4479,20 @@
       <c r="J92" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L92" t="s">
+        <v>98</v>
+      </c>
+      <c r="M92" t="s">
+        <v>62</v>
+      </c>
+      <c r="N92">
+        <v>9.4555840289537826E-2</v>
+      </c>
+      <c r="O92" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
         <v>70</v>
       </c>
@@ -3448,8 +4517,20 @@
       <c r="J93" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L93" t="s">
+        <v>98</v>
+      </c>
+      <c r="M93" t="s">
+        <v>63</v>
+      </c>
+      <c r="N93">
+        <v>0.11314463989373166</v>
+      </c>
+      <c r="O93" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="94" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
         <v>70</v>
       </c>
@@ -3474,8 +4555,20 @@
       <c r="J94" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L94" t="s">
+        <v>98</v>
+      </c>
+      <c r="M94" t="s">
+        <v>64</v>
+      </c>
+      <c r="N94">
+        <v>7.2773127536654422E-2</v>
+      </c>
+      <c r="O94" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="95" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
         <v>71</v>
       </c>
@@ -3500,8 +4593,20 @@
       <c r="J95" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L95" t="s">
+        <v>99</v>
+      </c>
+      <c r="M95" t="s">
+        <v>52</v>
+      </c>
+      <c r="N95">
+        <v>8.323301525084531E-2</v>
+      </c>
+      <c r="O95" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="96" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
         <v>71</v>
       </c>
@@ -3526,8 +4631,20 @@
       <c r="J96" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L96" t="s">
+        <v>99</v>
+      </c>
+      <c r="M96" t="s">
+        <v>54</v>
+      </c>
+      <c r="N96">
+        <v>0.11284606228257479</v>
+      </c>
+      <c r="O96" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
         <v>71</v>
       </c>
@@ -3552,8 +4669,20 @@
       <c r="J97" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L97" t="s">
+        <v>99</v>
+      </c>
+      <c r="M97" t="s">
+        <v>55</v>
+      </c>
+      <c r="N97">
+        <v>6.6110335513591273E-2</v>
+      </c>
+      <c r="O97" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
         <v>71</v>
       </c>
@@ -3578,8 +4707,20 @@
       <c r="J98" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L98" t="s">
+        <v>99</v>
+      </c>
+      <c r="M98" t="s">
+        <v>56</v>
+      </c>
+      <c r="N98">
+        <v>9.3641463347917855E-2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
         <v>71</v>
       </c>
@@ -3604,8 +4745,20 @@
       <c r="J99" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L99" t="s">
+        <v>99</v>
+      </c>
+      <c r="M99" t="s">
+        <v>57</v>
+      </c>
+      <c r="N99">
+        <v>0.11270458558232817</v>
+      </c>
+      <c r="O99" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="100" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
         <v>71</v>
       </c>
@@ -3630,8 +4783,20 @@
       <c r="J100" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L100" t="s">
+        <v>99</v>
+      </c>
+      <c r="M100" t="s">
+        <v>58</v>
+      </c>
+      <c r="N100">
+        <v>8.199796616653747E-2</v>
+      </c>
+      <c r="O100" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>71</v>
       </c>
@@ -3656,8 +4821,20 @@
       <c r="J101" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L101" t="s">
+        <v>99</v>
+      </c>
+      <c r="M101" t="s">
+        <v>59</v>
+      </c>
+      <c r="N101">
+        <v>4.4917749066644551E-2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="102" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>71</v>
       </c>
@@ -3682,8 +4859,20 @@
       <c r="J102" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L102" t="s">
+        <v>99</v>
+      </c>
+      <c r="M102" t="s">
+        <v>60</v>
+      </c>
+      <c r="N102">
+        <v>6.5174030011308073E-2</v>
+      </c>
+      <c r="O102" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
         <v>71</v>
       </c>
@@ -3708,8 +4897,20 @@
       <c r="J103" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L103" t="s">
+        <v>99</v>
+      </c>
+      <c r="M103" t="s">
+        <v>61</v>
+      </c>
+      <c r="N103">
+        <v>6.1595766792376522E-2</v>
+      </c>
+      <c r="O103" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="104" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
         <v>71</v>
       </c>
@@ -3734,8 +4935,20 @@
       <c r="J104" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L104" t="s">
+        <v>99</v>
+      </c>
+      <c r="M104" t="s">
+        <v>62</v>
+      </c>
+      <c r="N104">
+        <v>8.8369023746159056E-2</v>
+      </c>
+      <c r="O104" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="105" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
         <v>71</v>
       </c>
@@ -3760,8 +4973,20 @@
       <c r="J105" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L105" t="s">
+        <v>99</v>
+      </c>
+      <c r="M105" t="s">
+        <v>63</v>
+      </c>
+      <c r="N105">
+        <v>0.11405292932585455</v>
+      </c>
+      <c r="O105" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
         <v>71</v>
       </c>
@@ -3786,8 +5011,20 @@
       <c r="J106" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L106" t="s">
+        <v>99</v>
+      </c>
+      <c r="M106" t="s">
+        <v>64</v>
+      </c>
+      <c r="N106">
+        <v>7.5357072913863773E-2</v>
+      </c>
+      <c r="O106" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
         <v>72</v>
       </c>
@@ -3812,8 +5049,20 @@
       <c r="J107" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L107" t="s">
+        <v>100</v>
+      </c>
+      <c r="M107" t="s">
+        <v>52</v>
+      </c>
+      <c r="N107">
+        <v>8.9648259312651205E-2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
         <v>72</v>
       </c>
@@ -3838,8 +5087,20 @@
       <c r="J108" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L108" t="s">
+        <v>100</v>
+      </c>
+      <c r="M108" t="s">
+        <v>54</v>
+      </c>
+      <c r="N108">
+        <v>0.11566396577887829</v>
+      </c>
+      <c r="O108" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="109" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
         <v>72</v>
       </c>
@@ -3864,8 +5125,20 @@
       <c r="J109" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L109" t="s">
+        <v>100</v>
+      </c>
+      <c r="M109" t="s">
+        <v>55</v>
+      </c>
+      <c r="N109">
+        <v>6.6359681753599048E-2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="110" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
         <v>72</v>
       </c>
@@ -3890,8 +5163,20 @@
       <c r="J110" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L110" t="s">
+        <v>100</v>
+      </c>
+      <c r="M110" t="s">
+        <v>56</v>
+      </c>
+      <c r="N110">
+        <v>9.3267262231750289E-2</v>
+      </c>
+      <c r="O110" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
         <v>72</v>
       </c>
@@ -3916,8 +5201,20 @@
       <c r="J111" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L111" t="s">
+        <v>100</v>
+      </c>
+      <c r="M111" t="s">
+        <v>57</v>
+      </c>
+      <c r="N111">
+        <v>0.11145919994032891</v>
+      </c>
+      <c r="O111" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
         <v>72</v>
       </c>
@@ -3942,8 +5239,20 @@
       <c r="J112" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L112" t="s">
+        <v>100</v>
+      </c>
+      <c r="M112" t="s">
+        <v>58</v>
+      </c>
+      <c r="N112">
+        <v>8.1202406276482952E-2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
         <v>72</v>
       </c>
@@ -3968,8 +5277,20 @@
       <c r="J113" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L113" t="s">
+        <v>100</v>
+      </c>
+      <c r="M113" t="s">
+        <v>59</v>
+      </c>
+      <c r="N113">
+        <v>3.812021012642465E-2</v>
+      </c>
+      <c r="O113" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
         <v>72</v>
       </c>
@@ -3994,8 +5315,20 @@
       <c r="J114" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L114" t="s">
+        <v>100</v>
+      </c>
+      <c r="M114" t="s">
+        <v>60</v>
+      </c>
+      <c r="N114">
+        <v>7.2929580414246908E-2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
         <v>72</v>
       </c>
@@ -4020,8 +5353,20 @@
       <c r="J115" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L115" t="s">
+        <v>100</v>
+      </c>
+      <c r="M115" t="s">
+        <v>61</v>
+      </c>
+      <c r="N115">
+        <v>5.6196958498227596E-2</v>
+      </c>
+      <c r="O115" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
         <v>72</v>
       </c>
@@ -4046,8 +5391,20 @@
       <c r="J116" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L116" t="s">
+        <v>100</v>
+      </c>
+      <c r="M116" t="s">
+        <v>62</v>
+      </c>
+      <c r="N116">
+        <v>8.9874239582821008E-2</v>
+      </c>
+      <c r="O116" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +5429,20 @@
       <c r="J117" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L117" t="s">
+        <v>100</v>
+      </c>
+      <c r="M117" t="s">
+        <v>63</v>
+      </c>
+      <c r="N117">
+        <v>0.11542712213960635</v>
+      </c>
+      <c r="O117" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="118" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
         <v>72</v>
       </c>
@@ -4098,8 +5467,20 @@
       <c r="J118" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L118" t="s">
+        <v>100</v>
+      </c>
+      <c r="M118" t="s">
+        <v>64</v>
+      </c>
+      <c r="N118">
+        <v>6.9851113944980309E-2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="119" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +5505,20 @@
       <c r="J119" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L119" t="s">
+        <v>101</v>
+      </c>
+      <c r="M119" t="s">
+        <v>52</v>
+      </c>
+      <c r="N119">
+        <v>8.8937532827371088E-2</v>
+      </c>
+      <c r="O119" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="120" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
         <v>73</v>
       </c>
@@ -4150,8 +5543,20 @@
       <c r="J120" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L120" t="s">
+        <v>101</v>
+      </c>
+      <c r="M120" t="s">
+        <v>54</v>
+      </c>
+      <c r="N120">
+        <v>0.11118713979552354</v>
+      </c>
+      <c r="O120" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="121" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
         <v>73</v>
       </c>
@@ -4176,8 +5581,20 @@
       <c r="J121" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L121" t="s">
+        <v>101</v>
+      </c>
+      <c r="M121" t="s">
+        <v>55</v>
+      </c>
+      <c r="N121">
+        <v>7.0846681473502121E-2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="122" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
         <v>73</v>
       </c>
@@ -4202,8 +5619,20 @@
       <c r="J122" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L122" t="s">
+        <v>101</v>
+      </c>
+      <c r="M122" t="s">
+        <v>56</v>
+      </c>
+      <c r="N122">
+        <v>9.5496176187413531E-2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="123" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
         <v>73</v>
       </c>
@@ -4228,8 +5657,20 @@
       <c r="J123" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L123" t="s">
+        <v>101</v>
+      </c>
+      <c r="M123" t="s">
+        <v>57</v>
+      </c>
+      <c r="N123">
+        <v>0.11201433003819436</v>
+      </c>
+      <c r="O123" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="124" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
         <v>73</v>
       </c>
@@ -4254,8 +5695,20 @@
       <c r="J124" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L124" t="s">
+        <v>101</v>
+      </c>
+      <c r="M124" t="s">
+        <v>58</v>
+      </c>
+      <c r="N124">
+        <v>8.1738182382095292E-2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="125" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
         <v>73</v>
       </c>
@@ -4280,8 +5733,20 @@
       <c r="J125" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L125" t="s">
+        <v>101</v>
+      </c>
+      <c r="M125" t="s">
+        <v>59</v>
+      </c>
+      <c r="N125">
+        <v>5.4687876252347042E-2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="126" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
         <v>73</v>
       </c>
@@ -4306,8 +5771,20 @@
       <c r="J126" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L126" t="s">
+        <v>101</v>
+      </c>
+      <c r="M126" t="s">
+        <v>60</v>
+      </c>
+      <c r="N126">
+        <v>6.9186261432386764E-2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="127" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
         <v>73</v>
       </c>
@@ -4332,8 +5809,20 @@
       <c r="J127" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L127" t="s">
+        <v>101</v>
+      </c>
+      <c r="M127" t="s">
+        <v>61</v>
+      </c>
+      <c r="N127">
+        <v>6.2965620895656355E-2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="128" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
         <v>73</v>
       </c>
@@ -4358,8 +5847,20 @@
       <c r="J128" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L128" t="s">
+        <v>101</v>
+      </c>
+      <c r="M128" t="s">
+        <v>62</v>
+      </c>
+      <c r="N128">
+        <v>8.0609307064711547E-2</v>
+      </c>
+      <c r="O128" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="129" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
         <v>73</v>
       </c>
@@ -4384,8 +5885,20 @@
       <c r="J129" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L129" t="s">
+        <v>101</v>
+      </c>
+      <c r="M129" t="s">
+        <v>63</v>
+      </c>
+      <c r="N129">
+        <v>9.937606066956782E-2</v>
+      </c>
+      <c r="O129" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="130" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
         <v>73</v>
       </c>
@@ -4410,8 +5923,20 @@
       <c r="J130" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L130" t="s">
+        <v>101</v>
+      </c>
+      <c r="M130" t="s">
+        <v>64</v>
+      </c>
+      <c r="N130">
+        <v>7.2954830981232136E-2</v>
+      </c>
+      <c r="O130" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="131" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
         <v>74</v>
       </c>
@@ -4436,8 +5961,20 @@
       <c r="J131" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L131" t="s">
+        <v>102</v>
+      </c>
+      <c r="M131" t="s">
+        <v>52</v>
+      </c>
+      <c r="N131">
+        <v>8.9429643890422073E-2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
         <v>74</v>
       </c>
@@ -4462,8 +5999,20 @@
       <c r="J132" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L132" t="s">
+        <v>102</v>
+      </c>
+      <c r="M132" t="s">
+        <v>54</v>
+      </c>
+      <c r="N132">
+        <v>0.11264669510695621</v>
+      </c>
+      <c r="O132" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="133" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
         <v>74</v>
       </c>
@@ -4488,8 +6037,20 @@
       <c r="J133" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L133" t="s">
+        <v>102</v>
+      </c>
+      <c r="M133" t="s">
+        <v>55</v>
+      </c>
+      <c r="N133">
+        <v>6.7169023338673431E-2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="134" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
         <v>74</v>
       </c>
@@ -4514,8 +6075,20 @@
       <c r="J134" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L134" t="s">
+        <v>102</v>
+      </c>
+      <c r="M134" t="s">
+        <v>56</v>
+      </c>
+      <c r="N134">
+        <v>9.9234980660504568E-2</v>
+      </c>
+      <c r="O134" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="135" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
         <v>74</v>
       </c>
@@ -4540,8 +6113,20 @@
       <c r="J135" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L135" t="s">
+        <v>102</v>
+      </c>
+      <c r="M135" t="s">
+        <v>57</v>
+      </c>
+      <c r="N135">
+        <v>0.1096563528968658</v>
+      </c>
+      <c r="O135" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="136" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
         <v>74</v>
       </c>
@@ -4566,8 +6151,20 @@
       <c r="J136" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L136" t="s">
+        <v>102</v>
+      </c>
+      <c r="M136" t="s">
+        <v>58</v>
+      </c>
+      <c r="N136">
+        <v>8.9620736777971846E-2</v>
+      </c>
+      <c r="O136" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="137" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
         <v>74</v>
       </c>
@@ -4592,8 +6189,20 @@
       <c r="J137" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L137" t="s">
+        <v>102</v>
+      </c>
+      <c r="M137" t="s">
+        <v>59</v>
+      </c>
+      <c r="N137">
+        <v>5.4214685081387076E-2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
         <v>74</v>
       </c>
@@ -4618,8 +6227,20 @@
       <c r="J138" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L138" t="s">
+        <v>102</v>
+      </c>
+      <c r="M138" t="s">
+        <v>60</v>
+      </c>
+      <c r="N138">
+        <v>6.3045568965665086E-2</v>
+      </c>
+      <c r="O138" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="139" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
         <v>74</v>
       </c>
@@ -4644,8 +6265,20 @@
       <c r="J139" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L139" t="s">
+        <v>102</v>
+      </c>
+      <c r="M139" t="s">
+        <v>61</v>
+      </c>
+      <c r="N139">
+        <v>5.5675898857375679E-2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
         <v>74</v>
       </c>
@@ -4670,8 +6303,20 @@
       <c r="J140" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L140" t="s">
+        <v>102</v>
+      </c>
+      <c r="M140" t="s">
+        <v>62</v>
+      </c>
+      <c r="N140">
+        <v>8.0181665538439528E-2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
         <v>74</v>
       </c>
@@ -4696,8 +6341,20 @@
       <c r="J141" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L141" t="s">
+        <v>102</v>
+      </c>
+      <c r="M141" t="s">
+        <v>63</v>
+      </c>
+      <c r="N141">
+        <v>0.10336413630106216</v>
+      </c>
+      <c r="O141" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
         <v>74</v>
       </c>
@@ -4722,8 +6379,20 @@
       <c r="J142" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="L142" t="s">
+        <v>102</v>
+      </c>
+      <c r="M142" t="s">
+        <v>64</v>
+      </c>
+      <c r="N142">
+        <v>7.5760612584674994E-2</v>
+      </c>
+      <c r="O142" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="143" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
         <v>75</v>
       </c>
@@ -4749,7 +6418,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
         <v>75</v>
       </c>
@@ -5689,8 +7358,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890F21C7-EA8B-4C9E-9F8B-B2E90DB4728A}">
-  <dimension ref="B9:BL38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69A62DD-531B-47E4-9840-BA94A2B12359}">
+  <dimension ref="B9:BL49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:64" x14ac:dyDescent="0.45">
@@ -5888,15 +7557,15 @@
         <v>47</v>
       </c>
       <c r="BK10" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="BL10" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -5938,10 +7607,10 @@
         <v>0.94871794871794868</v>
       </c>
       <c r="Q11" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="R11" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -5980,10 +7649,10 @@
         <v>0.35565895715865664</v>
       </c>
       <c r="AF11" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -6022,7 +7691,7 @@
         <v>8.9891782309081472E-2</v>
       </c>
       <c r="AU11" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AV11">
         <v>0</v>
@@ -6061,13 +7730,13 @@
         <v>1.0779153517648195E-2</v>
       </c>
       <c r="BI11" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="BJ11" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK11" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL11">
         <v>0.49762387463701307</v>
@@ -6075,7 +7744,7 @@
     </row>
     <row r="12" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -6117,10 +7786,10 @@
         <v>0.94672982541447792</v>
       </c>
       <c r="Q12" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="R12" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="S12">
         <v>5.5520456436459207E-3</v>
@@ -6159,10 +7828,10 @@
         <v>1.1199628497169423E-2</v>
       </c>
       <c r="AF12" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AH12">
         <v>2.6727857083091694E-2</v>
@@ -6201,7 +7870,7 @@
         <v>2.8218881143468912E-2</v>
       </c>
       <c r="AU12" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AV12">
         <v>0</v>
@@ -6240,13 +7909,13 @@
         <v>1.0797103056501774E-2</v>
       </c>
       <c r="BI12" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="BJ12" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK12" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL12">
         <v>0.53686426066257731</v>
@@ -6254,7 +7923,7 @@
     </row>
     <row r="13" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -6295,8 +7964,92 @@
       <c r="O13">
         <v>0.93587744728512368</v>
       </c>
+      <c r="Q13" t="s">
+        <v>145</v>
+      </c>
+      <c r="R13" t="s">
+        <v>143</v>
+      </c>
+      <c r="S13">
+        <v>1.4646080316915734E-2</v>
+      </c>
+      <c r="T13">
+        <v>2.5000468398085899E-2</v>
+      </c>
+      <c r="U13">
+        <v>3.2123193947520362E-2</v>
+      </c>
+      <c r="V13">
+        <v>1.8673396166084523E-2</v>
+      </c>
+      <c r="W13">
+        <v>2.6067806267127642E-2</v>
+      </c>
+      <c r="X13">
+        <v>1.7051175837384275E-2</v>
+      </c>
+      <c r="Y13">
+        <v>3.2523849052048526E-2</v>
+      </c>
+      <c r="Z13">
+        <v>7.4188065033899853E-2</v>
+      </c>
+      <c r="AA13">
+        <v>2.645206048061171E-2</v>
+      </c>
+      <c r="AB13">
+        <v>2.1060927574859927E-2</v>
+      </c>
+      <c r="AC13">
+        <v>2.2962756677104897E-2</v>
+      </c>
+      <c r="AD13">
+        <v>1.608658229469451E-2</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH13">
+        <v>4.9833591642086922E-2</v>
+      </c>
+      <c r="AI13">
+        <v>3.8941088144525217E-2</v>
+      </c>
+      <c r="AJ13">
+        <v>5.1081065868119883E-2</v>
+      </c>
+      <c r="AK13">
+        <v>2.6442075903985736E-2</v>
+      </c>
+      <c r="AL13">
+        <v>4.2618205774820644E-2</v>
+      </c>
+      <c r="AM13">
+        <v>5.8338863574194495E-2</v>
+      </c>
+      <c r="AN13">
+        <v>4.8916721225804545E-2</v>
+      </c>
+      <c r="AO13">
+        <v>4.7186425803038307E-2</v>
+      </c>
+      <c r="AP13">
+        <v>7.4830438231398094E-2</v>
+      </c>
+      <c r="AQ13">
+        <v>2.5224627311293307E-2</v>
+      </c>
+      <c r="AR13">
+        <v>4.8924349410483785E-2</v>
+      </c>
+      <c r="AS13">
+        <v>4.8277768099231122E-2</v>
+      </c>
       <c r="AU13" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="AV13">
         <v>0</v>
@@ -6335,13 +8088,13 @@
         <v>1.2383658922181566E-2</v>
       </c>
       <c r="BI13" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="BJ13" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK13" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL13">
         <v>0.50067397194368091</v>
@@ -6349,7 +8102,7 @@
     </row>
     <row r="14" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -6391,7 +8144,7 @@
         <v>0.94139194139194149</v>
       </c>
       <c r="AU14" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AV14">
         <v>0</v>
@@ -6430,13 +8183,13 @@
         <v>1.0264029448276448E-2</v>
       </c>
       <c r="BI14" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="BJ14" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK14" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL14">
         <v>0.5230322600194991</v>
@@ -6444,7 +8197,7 @@
     </row>
     <row r="15" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -6486,7 +8239,7 @@
         <v>0.94469151785716066</v>
       </c>
       <c r="AU15" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AV15">
         <v>0</v>
@@ -6525,13 +8278,13 @@
         <v>9.5442785095935997E-3</v>
       </c>
       <c r="BI15" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="BJ15" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK15" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL15">
         <v>0.50626208669393846</v>
@@ -6539,7 +8292,7 @@
     </row>
     <row r="16" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -6581,7 +8334,7 @@
         <v>0.94505494505494503</v>
       </c>
       <c r="AU16" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="AV16">
         <v>0</v>
@@ -6620,13 +8373,13 @@
         <v>1.0793561696724322E-2</v>
       </c>
       <c r="BI16" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="BJ16" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK16" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL16">
         <v>0.54013240157412035</v>
@@ -6634,7 +8387,7 @@
     </row>
     <row r="17" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -6676,7 +8429,7 @@
         <v>0.94784241571834993</v>
       </c>
       <c r="AU17" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="AV17">
         <v>0</v>
@@ -6715,13 +8468,13 @@
         <v>9.8786985961523254E-3</v>
       </c>
       <c r="BI17" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="BJ17" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK17" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL17">
         <v>0.47587777340399484</v>
@@ -6729,7 +8482,7 @@
     </row>
     <row r="18" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -6771,7 +8524,7 @@
         <v>0.94898035687533633</v>
       </c>
       <c r="AU18" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="AV18">
         <v>0</v>
@@ -6810,13 +8563,13 @@
         <v>8.5077907478200571E-3</v>
       </c>
       <c r="BI18" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="BJ18" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK18" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL18">
         <v>0.46073873768976725</v>
@@ -6824,7 +8577,7 @@
     </row>
     <row r="19" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -6866,7 +8619,7 @@
         <v>0.95351288249357347</v>
       </c>
       <c r="AU19" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="AV19">
         <v>0</v>
@@ -6905,13 +8658,13 @@
         <v>6.9043313444517593E-3</v>
       </c>
       <c r="BI19" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="BJ19" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK19" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL19">
         <v>0.46994356737996101</v>
@@ -6919,7 +8672,7 @@
     </row>
     <row r="20" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -6961,7 +8714,7 @@
         <v>0.95238095238095222</v>
       </c>
       <c r="AU20" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="AV20">
         <v>0</v>
@@ -7000,13 +8753,13 @@
         <v>7.0277659844310714E-3</v>
       </c>
       <c r="BI20" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="BJ20" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK20" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL20">
         <v>0.46608129151093597</v>
@@ -7014,7 +8767,7 @@
     </row>
     <row r="21" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
@@ -7056,7 +8809,7 @@
         <v>0.95876463164067494</v>
       </c>
       <c r="AU21" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AV21">
         <v>0</v>
@@ -7095,13 +8848,13 @@
         <v>6.5915408835844329E-3</v>
       </c>
       <c r="BI21" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="BJ21" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK21" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL21">
         <v>0.47987128321927869</v>
@@ -7109,7 +8862,7 @@
     </row>
     <row r="22" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
         <v>31</v>
@@ -7151,7 +8904,7 @@
         <v>0.95787545787545803</v>
       </c>
       <c r="AU22" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="AV22">
         <v>0</v>
@@ -7190,13 +8943,13 @@
         <v>6.7805998452777046E-3</v>
       </c>
       <c r="BI22" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="BJ22" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK22" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL22">
         <v>0.48448741450274957</v>
@@ -7204,7 +8957,7 @@
     </row>
     <row r="23" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
         <v>31</v>
@@ -7246,7 +8999,7 @@
         <v>0.95238095238095222</v>
       </c>
       <c r="AU23" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AV23">
         <v>0</v>
@@ -7285,13 +9038,13 @@
         <v>7.7591097433076473E-3</v>
       </c>
       <c r="BI23" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="BJ23" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK23" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL23">
         <v>0.4701524521623156</v>
@@ -7299,7 +9052,7 @@
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -7341,7 +9094,7 @@
         <v>0.95238095238095255</v>
       </c>
       <c r="AU24" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AV24">
         <v>0</v>
@@ -7380,13 +9133,13 @@
         <v>7.5885077415074713E-3</v>
       </c>
       <c r="BI24" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="BJ24" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK24" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL24">
         <v>0.47880717919369542</v>
@@ -7394,7 +9147,7 @@
     </row>
     <row r="25" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
@@ -7436,7 +9189,7 @@
         <v>0.95238095238095244</v>
       </c>
       <c r="AU25" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AV25">
         <v>0</v>
@@ -7475,13 +9228,13 @@
         <v>8.0254421086847962E-3</v>
       </c>
       <c r="BI25" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="BJ25" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK25" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL25">
         <v>0.47540615471211939</v>
@@ -7489,94 +9242,94 @@
     </row>
     <row r="26" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26">
-        <v>0.57892190762383655</v>
+        <v>0.50672728644774723</v>
       </c>
       <c r="E26">
-        <v>0.56216904285346725</v>
+        <v>0.52179503639943625</v>
       </c>
       <c r="F26">
-        <v>0.55870245101859362</v>
+        <v>0.51016758655205452</v>
       </c>
       <c r="G26">
-        <v>0.48945563530226327</v>
+        <v>0.46905754865473892</v>
       </c>
       <c r="H26">
-        <v>0.49440816120851466</v>
+        <v>0.52306535602133741</v>
       </c>
       <c r="I26">
-        <v>0.49750342020096566</v>
+        <v>0.47156056622516657</v>
       </c>
       <c r="J26">
-        <v>0.52028533989392423</v>
+        <v>0.48168509151808964</v>
       </c>
       <c r="K26">
-        <v>0.43839216163427236</v>
+        <v>0.5630036416474069</v>
       </c>
       <c r="L26">
-        <v>0.44065900741441466</v>
+        <v>0.50485159815134439</v>
       </c>
       <c r="M26">
-        <v>0.47315479675709554</v>
+        <v>0.47852145634499094</v>
       </c>
       <c r="N26">
-        <v>0.53658903468160213</v>
+        <v>0.52219055816136928</v>
       </c>
       <c r="O26">
-        <v>0.5219669785564951</v>
+        <v>0.49806953967362466</v>
       </c>
       <c r="AU26" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AV26">
-        <v>0.20369351340667513</v>
+        <v>0.26104488818861477</v>
       </c>
       <c r="AW26">
-        <v>0.19499495486185872</v>
+        <v>0.24507714414300974</v>
       </c>
       <c r="AX26">
-        <v>0.19761383006092689</v>
+        <v>0.25475420521895736</v>
       </c>
       <c r="AY26">
-        <v>0.17473946650348862</v>
+        <v>0.28556891539186685</v>
       </c>
       <c r="AZ26">
-        <v>0.17587255991018572</v>
+        <v>0.21316516224074433</v>
       </c>
       <c r="BA26">
-        <v>0.18834831231650784</v>
+        <v>0.27612964874762386</v>
       </c>
       <c r="BB26">
-        <v>7.530668772631699E-2</v>
+        <v>0.1559958675484048</v>
       </c>
       <c r="BC26">
-        <v>9.0415882556690738E-2</v>
+        <v>8.7741666517800215E-2</v>
       </c>
       <c r="BD26">
-        <v>9.8042378087678766E-2</v>
+        <v>0.11859960294752697</v>
       </c>
       <c r="BE26">
-        <v>0.15106391846804648</v>
+        <v>0.27523184500391246</v>
       </c>
       <c r="BF26">
-        <v>0.15419540507108895</v>
+        <v>0.24945818659185104</v>
       </c>
       <c r="BG26">
-        <v>0.15252987562976719</v>
+        <v>0.28556733050120719</v>
       </c>
       <c r="BI26" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="BJ26" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK26" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL26">
         <v>0.20369351340667513</v>
@@ -7584,94 +9337,94 @@
     </row>
     <row r="27" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
       </c>
       <c r="D27">
-        <v>0.57328104245571632</v>
+        <v>0.4796558152466151</v>
       </c>
       <c r="E27">
-        <v>0.56879098077204326</v>
+        <v>0.50036692976419683</v>
       </c>
       <c r="F27">
-        <v>0.57408446194727292</v>
+        <v>0.46577915609221748</v>
       </c>
       <c r="G27">
-        <v>0.55137474583665969</v>
+        <v>0.43126153672200973</v>
       </c>
       <c r="H27">
-        <v>0.52967706923765845</v>
+        <v>0.4578780635034585</v>
       </c>
       <c r="I27">
-        <v>0.53283390336404068</v>
+        <v>0.39712955489470675</v>
       </c>
       <c r="J27">
-        <v>0.55576830981822489</v>
+        <v>0.39105743306744273</v>
       </c>
       <c r="K27">
-        <v>0.48846160326515076</v>
+        <v>0.45493338627802038</v>
       </c>
       <c r="L27">
-        <v>0.4442402467977854</v>
+        <v>0.37220395468294304</v>
       </c>
       <c r="M27">
-        <v>0.53261676360763432</v>
+        <v>0.45035911178268606</v>
       </c>
       <c r="N27">
-        <v>0.55541016763651696</v>
+        <v>0.50305819528696805</v>
       </c>
       <c r="O27">
-        <v>0.52900572458623485</v>
+        <v>0.44202237787266102</v>
       </c>
       <c r="AU27" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AV27">
-        <v>0.2186337042324776</v>
+        <v>0.30136436759875856</v>
       </c>
       <c r="AW27">
-        <v>0.20872767166693784</v>
+        <v>0.29607686596814092</v>
       </c>
       <c r="AX27">
-        <v>0.20835778653156878</v>
+        <v>0.30552099831703183</v>
       </c>
       <c r="AY27">
-        <v>0.19228122880192089</v>
+        <v>0.32619905115484077</v>
       </c>
       <c r="AZ27">
-        <v>0.19973958333187924</v>
+        <v>0.28542047300203854</v>
       </c>
       <c r="BA27">
-        <v>0.20485700014958377</v>
+        <v>0.37991305316373924</v>
       </c>
       <c r="BB27">
-        <v>6.3480275130860131E-2</v>
+        <v>0.19312275585171768</v>
       </c>
       <c r="BC27">
-        <v>8.372217419027371E-2</v>
+        <v>0.19595779517090808</v>
       </c>
       <c r="BD27">
-        <v>0.10317446330459316</v>
+        <v>0.26627992396657463</v>
       </c>
       <c r="BE27">
-        <v>0.19724068420119856</v>
+        <v>0.28410712446640546</v>
       </c>
       <c r="BF27">
-        <v>0.18422254047343278</v>
+        <v>0.28546636886948595</v>
       </c>
       <c r="BG27">
-        <v>0.18883137089035512</v>
+        <v>0.31516897799696342</v>
       </c>
       <c r="BI27" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="BJ27" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK27" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL27">
         <v>0.2186337042324776</v>
@@ -7679,94 +9432,94 @@
     </row>
     <row r="28" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
       </c>
       <c r="D28">
-        <v>0.52705410088583815</v>
+        <v>0.52213328562796013</v>
       </c>
       <c r="E28">
-        <v>0.55642496977544753</v>
+        <v>0.53001388168686514</v>
       </c>
       <c r="F28">
-        <v>0.54371133154559348</v>
+        <v>0.51027468056906822</v>
       </c>
       <c r="G28">
-        <v>0.47204817080521755</v>
+        <v>0.43377997112270733</v>
       </c>
       <c r="H28">
-        <v>0.54511938842890284</v>
+        <v>0.49070775769725966</v>
       </c>
       <c r="I28">
-        <v>0.4949264794500049</v>
+        <v>0.44102023442417948</v>
       </c>
       <c r="J28">
-        <v>0.54982485496735034</v>
+        <v>0.43238883880498002</v>
       </c>
       <c r="K28">
-        <v>0.58794929913672922</v>
+        <v>0.50744944288127081</v>
       </c>
       <c r="L28">
-        <v>0.61726975139200624</v>
+        <v>0.40431617585181989</v>
       </c>
       <c r="M28">
-        <v>0.51914580653983899</v>
+        <v>0.49179393594787724</v>
       </c>
       <c r="N28">
-        <v>0.53131062499106452</v>
+        <v>0.5256818504187617</v>
       </c>
       <c r="O28">
-        <v>0.51624643311855101</v>
+        <v>0.50108684978687723</v>
       </c>
       <c r="AU28" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="AV28">
-        <v>0.26947615458344037</v>
+        <v>0.28370114688398157</v>
       </c>
       <c r="AW28">
-        <v>0.24194009927589816</v>
+        <v>0.29121166497492362</v>
       </c>
       <c r="AX28">
-        <v>0.25023034133264255</v>
+        <v>0.29736594156531193</v>
       </c>
       <c r="AY28">
-        <v>0.23238795446024321</v>
+        <v>0.34213719471866261</v>
       </c>
       <c r="AZ28">
-        <v>0.20106531312443676</v>
+        <v>0.26811187624336041</v>
       </c>
       <c r="BA28">
-        <v>0.22405546674378485</v>
+        <v>0.3404436916818005</v>
       </c>
       <c r="BB28">
-        <v>0.15374964426566418</v>
+        <v>0.1517984579004123</v>
       </c>
       <c r="BC28">
-        <v>0.10351524482199274</v>
+        <v>0.1403943571730864</v>
       </c>
       <c r="BD28">
-        <v>9.9911550324906631E-2</v>
+        <v>0.22516824063291627</v>
       </c>
       <c r="BE28">
-        <v>0.25157142879393224</v>
+        <v>0.23134364147792769</v>
       </c>
       <c r="BF28">
-        <v>0.25758623738923847</v>
+        <v>0.2316642418696776</v>
       </c>
       <c r="BG28">
-        <v>0.26487324156774861</v>
+        <v>0.26862099544813656</v>
       </c>
       <c r="BI28" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="BJ28" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK28" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL28">
         <v>0.26947615458344037</v>
@@ -7774,94 +9527,94 @@
     </row>
     <row r="29" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
       </c>
       <c r="D29">
-        <v>0.53496725529204692</v>
+        <v>0.52701527131267056</v>
       </c>
       <c r="E29">
-        <v>0.54859048834673718</v>
+        <v>0.51629069450262532</v>
       </c>
       <c r="F29">
-        <v>0.5309255994311155</v>
+        <v>0.49310233025199895</v>
       </c>
       <c r="G29">
-        <v>0.51939031581564188</v>
+        <v>0.44491278298180065</v>
       </c>
       <c r="H29">
-        <v>0.52646027747227309</v>
+        <v>0.47332287871608686</v>
       </c>
       <c r="I29">
-        <v>0.5472588150175397</v>
+        <v>0.43366405762001309</v>
       </c>
       <c r="J29">
-        <v>0.5918672556049257</v>
+        <v>0.43848649384735716</v>
       </c>
       <c r="K29">
-        <v>0.54502308404774547</v>
+        <v>0.47074333541670477</v>
       </c>
       <c r="L29">
-        <v>0.64237137992239413</v>
+        <v>0.37222953417005272</v>
       </c>
       <c r="M29">
-        <v>0.54731096377687249</v>
+        <v>0.46319106528091125</v>
       </c>
       <c r="N29">
-        <v>0.53287758101686633</v>
+        <v>0.50082401349920658</v>
       </c>
       <c r="O29">
-        <v>0.54411512439006648</v>
+        <v>0.47836406532525927</v>
       </c>
       <c r="AU29" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AV29">
-        <v>0.14984587266811897</v>
+        <v>0.28561693146074124</v>
       </c>
       <c r="AW29">
-        <v>0.13602056818009348</v>
+        <v>0.28514426992703951</v>
       </c>
       <c r="AX29">
-        <v>0.14600372150251845</v>
+        <v>0.28721608901506546</v>
       </c>
       <c r="AY29">
-        <v>9.0828534798825064E-2</v>
+        <v>0.33045820716101437</v>
       </c>
       <c r="AZ29">
-        <v>0.10966575677036557</v>
+        <v>0.28360586614615141</v>
       </c>
       <c r="BA29">
-        <v>9.4847115738401155E-2</v>
+        <v>0.36452403159933444</v>
       </c>
       <c r="BB29">
-        <v>5.372129455490162E-2</v>
+        <v>0.17530892095052014</v>
       </c>
       <c r="BC29">
-        <v>7.9911802576982202E-2</v>
+        <v>0.19713341630084297</v>
       </c>
       <c r="BD29">
-        <v>5.1721956758200079E-2</v>
+        <v>0.24202196505243295</v>
       </c>
       <c r="BE29">
-        <v>0.11809070232445909</v>
+        <v>0.2740429768554335</v>
       </c>
       <c r="BF29">
-        <v>0.14092658017829146</v>
+        <v>0.25849367530206663</v>
       </c>
       <c r="BG29">
-        <v>0.11829073459395303</v>
+        <v>0.28734021616628874</v>
       </c>
       <c r="BI29" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="BJ29" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK29" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL29">
         <v>0.14984587266811897</v>
@@ -7869,94 +9622,94 @@
     </row>
     <row r="30" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
       </c>
       <c r="D30">
-        <v>0.46875530612657806</v>
+        <v>0.45073142776032438</v>
       </c>
       <c r="E30">
-        <v>0.51693528458148885</v>
+        <v>0.4669215907571227</v>
       </c>
       <c r="F30">
-        <v>0.48072250116858939</v>
+        <v>0.46450226408742051</v>
       </c>
       <c r="G30">
-        <v>0.50123349140010887</v>
+        <v>0.49400111515148537</v>
       </c>
       <c r="H30">
-        <v>0.54115582969230014</v>
+        <v>0.50521997080121628</v>
       </c>
       <c r="I30">
-        <v>0.53837280679671495</v>
+        <v>0.47784636949455223</v>
       </c>
       <c r="J30">
-        <v>0.5323633471868966</v>
+        <v>0.46557195875258156</v>
       </c>
       <c r="K30">
-        <v>0.50767143019232697</v>
+        <v>0.47178237023973957</v>
       </c>
       <c r="L30">
-        <v>0.48109271224314643</v>
+        <v>0.44521107385150727</v>
       </c>
       <c r="M30">
-        <v>0.48585808579285983</v>
+        <v>0.49331432095815331</v>
       </c>
       <c r="N30">
-        <v>0.51660760910353021</v>
+        <v>0.49003941120850303</v>
       </c>
       <c r="O30">
-        <v>0.47376573622842516</v>
+        <v>0.45213532440192511</v>
       </c>
       <c r="AU30" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AV30">
-        <v>0.28504526951035125</v>
+        <v>0.26436733667458484</v>
       </c>
       <c r="AW30">
-        <v>0.23241706671233073</v>
+        <v>0.24946032578883506</v>
       </c>
       <c r="AX30">
-        <v>0.26541730182654477</v>
+        <v>0.27322828288243717</v>
       </c>
       <c r="AY30">
-        <v>0.19958730917235032</v>
+        <v>0.25388031873301603</v>
       </c>
       <c r="AZ30">
-        <v>0.19835987200837721</v>
+        <v>0.251483198909629</v>
       </c>
       <c r="BA30">
-        <v>0.17545198604711298</v>
+        <v>0.2702893607307788</v>
       </c>
       <c r="BB30">
-        <v>0.11957950025971902</v>
+        <v>0.13726541163542788</v>
       </c>
       <c r="BC30">
-        <v>0.11724510515813562</v>
+        <v>0.15293692511149165</v>
       </c>
       <c r="BD30">
-        <v>0.12605491550782819</v>
+        <v>0.20206559691898665</v>
       </c>
       <c r="BE30">
-        <v>0.2045797141901097</v>
+        <v>0.23262277176466342</v>
       </c>
       <c r="BF30">
-        <v>0.18280890097467858</v>
+        <v>0.23316673830740536</v>
       </c>
       <c r="BG30">
-        <v>0.2052346236346112</v>
+        <v>0.24469762569427214</v>
       </c>
       <c r="BI30" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="BJ30" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK30" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL30">
         <v>0.28504526951035125</v>
@@ -7964,94 +9717,94 @@
     </row>
     <row r="31" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
       </c>
       <c r="D31">
-        <v>0.54899173912775678</v>
+        <v>0.46130471038971615</v>
       </c>
       <c r="E31">
-        <v>0.56465514685904783</v>
+        <v>0.46645343557890867</v>
       </c>
       <c r="F31">
-        <v>0.55949219755217339</v>
+        <v>0.44977058693739891</v>
       </c>
       <c r="G31">
-        <v>0.57129752125963373</v>
+        <v>0.50138352840180211</v>
       </c>
       <c r="H31">
-        <v>0.60620383024656965</v>
+        <v>0.49181435947455837</v>
       </c>
       <c r="I31">
-        <v>0.60870922265287131</v>
+        <v>0.46751900148993059</v>
       </c>
       <c r="J31">
-        <v>0.63417784407654787</v>
+        <v>0.47004319466228239</v>
       </c>
       <c r="K31">
-        <v>0.58254252491701219</v>
+        <v>0.44566256207478316</v>
       </c>
       <c r="L31">
-        <v>0.60232715098902123</v>
+        <v>0.39566960465314971</v>
       </c>
       <c r="M31">
-        <v>0.55614056152757307</v>
+        <v>0.45454585797423769</v>
       </c>
       <c r="N31">
-        <v>0.5608524853425878</v>
+        <v>0.46140854465281922</v>
       </c>
       <c r="O31">
-        <v>0.53572907378539947</v>
+        <v>0.41680534557468207</v>
       </c>
       <c r="AU31" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="AV31">
-        <v>0.14817382942767271</v>
+        <v>0.30058472014736021</v>
       </c>
       <c r="AW31">
-        <v>0.12961546165317836</v>
+        <v>0.28003757441780008</v>
       </c>
       <c r="AX31">
-        <v>0.133261330786835</v>
+        <v>0.31326665298353806</v>
       </c>
       <c r="AY31">
-        <v>0.11609753306985576</v>
+        <v>0.27916877611543633</v>
       </c>
       <c r="AZ31">
-        <v>0.11979077951729598</v>
+        <v>0.27655626110867026</v>
       </c>
       <c r="BA31">
-        <v>0.11205738127221894</v>
+        <v>0.29389812815202854</v>
       </c>
       <c r="BB31">
-        <v>3.3348814493915198E-2</v>
+        <v>0.15104400981486016</v>
       </c>
       <c r="BC31">
-        <v>5.9832806113654845E-2</v>
+        <v>0.17495881155934639</v>
       </c>
       <c r="BD31">
-        <v>3.7629637330862366E-2</v>
+        <v>0.23811525229803318</v>
       </c>
       <c r="BE31">
-        <v>0.11136928057072905</v>
+        <v>0.27258630136861028</v>
       </c>
       <c r="BF31">
-        <v>0.10582348124556699</v>
+        <v>0.26611832337281432</v>
       </c>
       <c r="BG31">
-        <v>0.11121142306366208</v>
+        <v>0.28646524716367189</v>
       </c>
       <c r="BI31" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="BJ31" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK31" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL31">
         <v>0.14817382942767271</v>
@@ -8059,94 +9812,94 @@
     </row>
     <row r="32" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.47386780387881305</v>
+        <v>0.52601043897839428</v>
       </c>
       <c r="E32">
-        <v>0.51330726620812894</v>
+        <v>0.51757523551125673</v>
       </c>
       <c r="F32">
-        <v>0.47792483467379276</v>
+        <v>0.50330299373845744</v>
       </c>
       <c r="G32">
-        <v>0.52141007579705168</v>
+        <v>0.51302212598598818</v>
       </c>
       <c r="H32">
-        <v>0.52160449380856155</v>
+        <v>0.50085104501897959</v>
       </c>
       <c r="I32">
-        <v>0.5389018496341037</v>
+        <v>0.46234765882721007</v>
       </c>
       <c r="J32">
-        <v>0.5403754950926476</v>
+        <v>0.48665635393632994</v>
       </c>
       <c r="K32">
-        <v>0.53919002807501759</v>
+        <v>0.47166764250952331</v>
       </c>
       <c r="L32">
-        <v>0.53162483170196762</v>
+        <v>0.37911642329762701</v>
       </c>
       <c r="M32">
-        <v>0.4860408503251244</v>
+        <v>0.48874449622295313</v>
       </c>
       <c r="N32">
-        <v>0.48686830370897549</v>
+        <v>0.50584098764808849</v>
       </c>
       <c r="O32">
-        <v>0.46872525783728464</v>
+        <v>0.45057651009822347</v>
       </c>
       <c r="AU32" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="AV32">
-        <v>0.16694453608547899</v>
+        <v>0.25649435934773451</v>
       </c>
       <c r="AW32">
-        <v>0.15000189571173506</v>
+        <v>0.26069063355575267</v>
       </c>
       <c r="AX32">
-        <v>0.15258825424762915</v>
+        <v>0.27076636700096063</v>
       </c>
       <c r="AY32">
-        <v>0.12348236416897743</v>
+        <v>0.261298691177894</v>
       </c>
       <c r="AZ32">
-        <v>0.1584069430929208</v>
+        <v>0.25565539553445188</v>
       </c>
       <c r="BA32">
-        <v>0.12191438118184995</v>
+        <v>0.28371331253019821</v>
       </c>
       <c r="BB32">
-        <v>5.9451421126396474E-2</v>
+        <v>0.10516456361380991</v>
       </c>
       <c r="BC32">
-        <v>0.10796079978461877</v>
+        <v>0.1218948538181877</v>
       </c>
       <c r="BD32">
-        <v>7.1748862572750566E-2</v>
+        <v>0.1821919421969157</v>
       </c>
       <c r="BE32">
-        <v>0.11894229390178822</v>
+        <v>0.25989541301862551</v>
       </c>
       <c r="BF32">
-        <v>0.13287140056803814</v>
+        <v>0.24879074905141454</v>
       </c>
       <c r="BG32">
-        <v>0.11858382003111445</v>
+        <v>0.26669816805084356</v>
       </c>
       <c r="BI32" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="BJ32" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK32" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL32">
         <v>0.16694453608547899</v>
@@ -8154,94 +9907,94 @@
     </row>
     <row r="33" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
       </c>
       <c r="D33">
-        <v>0.48185553843964513</v>
+        <v>0.50221953347544579</v>
       </c>
       <c r="E33">
-        <v>0.56964786342726559</v>
+        <v>0.50858570492696387</v>
       </c>
       <c r="F33">
-        <v>0.44832426131563591</v>
+        <v>0.4973384483072335</v>
       </c>
       <c r="G33">
-        <v>0.47170772428678942</v>
+        <v>0.49043582657887452</v>
       </c>
       <c r="H33">
-        <v>0.55759870443478099</v>
+        <v>0.48645091968906456</v>
       </c>
       <c r="I33">
-        <v>0.40537401206637347</v>
+        <v>0.4219253703951768</v>
       </c>
       <c r="J33">
-        <v>0.4652699180465466</v>
+        <v>0.44584436041480485</v>
       </c>
       <c r="K33">
-        <v>0.55910718442183105</v>
+        <v>0.49659607403261979</v>
       </c>
       <c r="L33">
-        <v>0.41684138098023105</v>
+        <v>0.39485714083043183</v>
       </c>
       <c r="M33">
-        <v>0.47617387723311899</v>
+        <v>0.48209799671410958</v>
       </c>
       <c r="N33">
-        <v>0.56043981496736084</v>
+        <v>0.50787277117666063</v>
       </c>
       <c r="O33">
-        <v>0.43596938013381753</v>
+        <v>0.44530090246984022</v>
       </c>
       <c r="AU33" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AV33">
-        <v>0.15876763548459355</v>
+        <v>0.2599258422818756</v>
       </c>
       <c r="AW33">
-        <v>0.10576978818192537</v>
+        <v>0.28192281823353366</v>
       </c>
       <c r="AX33">
-        <v>0.14992170591636053</v>
+        <v>0.27527193129824906</v>
       </c>
       <c r="AY33">
-        <v>0.1321696570218425</v>
+        <v>0.28607289171033612</v>
       </c>
       <c r="AZ33">
-        <v>0.12035742658568196</v>
+        <v>0.27544829441000895</v>
       </c>
       <c r="BA33">
-        <v>0.14379396175678688</v>
+        <v>0.33400297200217077</v>
       </c>
       <c r="BB33">
-        <v>8.527668233543502E-2</v>
+        <v>0.13722287013896792</v>
       </c>
       <c r="BC33">
-        <v>6.0448357068224101E-2</v>
+        <v>0.15928433890853499</v>
       </c>
       <c r="BD33">
-        <v>9.0955994304572491E-2</v>
+        <v>0.25089852996624779</v>
       </c>
       <c r="BE33">
-        <v>0.12235518373597128</v>
+        <v>0.27293234480425399</v>
       </c>
       <c r="BF33">
-        <v>0.10226014148695747</v>
+        <v>0.28180674279817286</v>
       </c>
       <c r="BG33">
-        <v>0.13178530217096121</v>
+        <v>0.31032567350064499</v>
       </c>
       <c r="BI33" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="BJ33" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK33" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL33">
         <v>0.15876763548459355</v>
@@ -8249,94 +10002,94 @@
     </row>
     <row r="34" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
       </c>
       <c r="D34">
-        <v>0.43889105811303908</v>
+        <v>0.52876858818737327</v>
       </c>
       <c r="E34">
-        <v>0.54996770753102719</v>
+        <v>0.51471672421879999</v>
       </c>
       <c r="F34">
-        <v>0.41499659614663975</v>
+        <v>0.50753141778852939</v>
       </c>
       <c r="G34">
-        <v>0.41699593648517574</v>
+        <v>0.48876692226890261</v>
       </c>
       <c r="H34">
-        <v>0.53205515618654753</v>
+        <v>0.49088153317630795</v>
       </c>
       <c r="I34">
-        <v>0.39549973166085894</v>
+        <v>0.43760757871353684</v>
       </c>
       <c r="J34">
-        <v>0.41817749638207752</v>
+        <v>0.45495710620481433</v>
       </c>
       <c r="K34">
-        <v>0.56679185279610034</v>
+        <v>0.50194486462826049</v>
       </c>
       <c r="L34">
-        <v>0.41511669086440778</v>
+        <v>0.36641604381695242</v>
       </c>
       <c r="M34">
-        <v>0.42973688467532861</v>
+        <v>0.48546756991985929</v>
       </c>
       <c r="N34">
-        <v>0.52460575089762518</v>
+        <v>0.51675823111984043</v>
       </c>
       <c r="O34">
-        <v>0.39199195731259823</v>
+        <v>0.47535734284014447</v>
       </c>
       <c r="AU34" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="AV34">
-        <v>0.2081188959446553</v>
+        <v>0.26468890229749381</v>
       </c>
       <c r="AW34">
-        <v>0.14455049442503548</v>
+        <v>0.27320078156222077</v>
       </c>
       <c r="AX34">
-        <v>0.21169627590616868</v>
+        <v>0.26123833234231281</v>
       </c>
       <c r="AY34">
-        <v>0.1650032669157942</v>
+        <v>0.26938771236660985</v>
       </c>
       <c r="AZ34">
-        <v>0.13820612539089708</v>
+        <v>0.25754579410322903</v>
       </c>
       <c r="BA34">
-        <v>0.17419706887386943</v>
+        <v>0.31272038286604792</v>
       </c>
       <c r="BB34">
-        <v>0.11548166212981592</v>
+        <v>0.11010418827750444</v>
       </c>
       <c r="BC34">
-        <v>7.0704672104585906E-2</v>
+        <v>0.16851643212456285</v>
       </c>
       <c r="BD34">
-        <v>0.11726975310119528</v>
+        <v>0.21642134985059838</v>
       </c>
       <c r="BE34">
-        <v>0.16996208614188521</v>
+        <v>0.26244011387175115</v>
       </c>
       <c r="BF34">
-        <v>0.13152649001402134</v>
+        <v>0.26964529296777145</v>
       </c>
       <c r="BG34">
-        <v>0.17860347381011976</v>
+        <v>0.27196127066564257</v>
       </c>
       <c r="BI34" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="BJ34" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK34" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL34">
         <v>0.21169627590616868</v>
@@ -8344,94 +10097,94 @@
     </row>
     <row r="35" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
       </c>
       <c r="D35">
-        <v>0.46005603239494119</v>
+        <v>0.48268009485938596</v>
       </c>
       <c r="E35">
-        <v>0.53675089926147979</v>
+        <v>0.48216432855389901</v>
       </c>
       <c r="F35">
-        <v>0.45931862125680684</v>
+        <v>0.4897512810170831</v>
       </c>
       <c r="G35">
-        <v>0.4480715206538039</v>
+        <v>0.50819920830553633</v>
       </c>
       <c r="H35">
-        <v>0.56117120800424969</v>
+        <v>0.49542773425166431</v>
       </c>
       <c r="I35">
-        <v>0.41218917588748211</v>
+        <v>0.46297289769430078</v>
       </c>
       <c r="J35">
-        <v>0.50519506433685613</v>
+        <v>0.47167703778327896</v>
       </c>
       <c r="K35">
-        <v>0.60358158247437199</v>
+        <v>0.49066857597183183</v>
       </c>
       <c r="L35">
-        <v>0.45222485075627655</v>
+        <v>0.45021847625379785</v>
       </c>
       <c r="M35">
-        <v>0.49042295663712754</v>
+        <v>0.48524615348750333</v>
       </c>
       <c r="N35">
-        <v>0.57454003676448273</v>
+        <v>0.49429563944058563</v>
       </c>
       <c r="O35">
-        <v>0.44085219496445044</v>
+        <v>0.43972346563254566</v>
       </c>
       <c r="AU35" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="AV35">
-        <v>0.14013308658561607</v>
+        <v>0.26880654320699693</v>
       </c>
       <c r="AW35">
-        <v>9.4577599922550923E-2</v>
+        <v>0.26884335328276293</v>
       </c>
       <c r="AX35">
-        <v>0.15062430379992675</v>
+        <v>0.28550453243842588</v>
       </c>
       <c r="AY35">
-        <v>0.13271230088904068</v>
+        <v>0.28235496082286754</v>
       </c>
       <c r="AZ35">
-        <v>9.6179275635501285E-2</v>
+        <v>0.2649555450887483</v>
       </c>
       <c r="BA35">
-        <v>0.13755388150587203</v>
+        <v>0.3222353285844029</v>
       </c>
       <c r="BB35">
-        <v>7.7506812960281501E-2</v>
+        <v>0.16169645501211666</v>
       </c>
       <c r="BC35">
-        <v>5.2168417347353904E-2</v>
+        <v>0.16365123644644508</v>
       </c>
       <c r="BD35">
-        <v>0.10550855423420852</v>
+        <v>0.24822851386621028</v>
       </c>
       <c r="BE35">
-        <v>0.13731834713686256</v>
+        <v>0.24095784100796158</v>
       </c>
       <c r="BF35">
-        <v>0.10430301311530919</v>
+        <v>0.2376444298928643</v>
       </c>
       <c r="BG35">
-        <v>0.14399773360194409</v>
+        <v>0.29076937811868864</v>
       </c>
       <c r="BI35" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="BJ35" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK35" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL35">
         <v>0.15062430379992675</v>
@@ -8439,94 +10192,94 @@
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
       </c>
       <c r="D36">
-        <v>0.52924742569917493</v>
+        <v>0.4890699668502726</v>
       </c>
       <c r="E36">
-        <v>0.58075903976353449</v>
+        <v>0.47741868960467915</v>
       </c>
       <c r="F36">
-        <v>0.53836328139037992</v>
+        <v>0.48585109057506332</v>
       </c>
       <c r="G36">
-        <v>0.52351877866556784</v>
+        <v>0.45201709859742045</v>
       </c>
       <c r="H36">
-        <v>0.57131800339146077</v>
+        <v>0.47918177287314151</v>
       </c>
       <c r="I36">
-        <v>0.46050445061372136</v>
+        <v>0.4238933968011851</v>
       </c>
       <c r="J36">
-        <v>0.61809686081619386</v>
+        <v>0.44163667849376315</v>
       </c>
       <c r="K36">
-        <v>0.59621972436891857</v>
+        <v>0.47662694507814279</v>
       </c>
       <c r="L36">
-        <v>0.50712111620686096</v>
+        <v>0.46896069068792495</v>
       </c>
       <c r="M36">
-        <v>0.54877734650392596</v>
+        <v>0.46971220078535952</v>
       </c>
       <c r="N36">
-        <v>0.59288587818348848</v>
+        <v>0.50168853673953051</v>
       </c>
       <c r="O36">
-        <v>0.52207926199718191</v>
+        <v>0.44826862235865261</v>
       </c>
       <c r="AU36" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="AV36">
-        <v>0.14013315443927093</v>
+        <v>0.28951438199192064</v>
       </c>
       <c r="AW36">
-        <v>0.11678027147943203</v>
+        <v>0.29174074187107957</v>
       </c>
       <c r="AX36">
-        <v>0.14361851742774945</v>
+        <v>0.28993217364217705</v>
       </c>
       <c r="AY36">
-        <v>0.12768068970596627</v>
+        <v>0.3142737537099437</v>
       </c>
       <c r="AZ36">
-        <v>0.11741801186073036</v>
+        <v>0.27782230349549442</v>
       </c>
       <c r="BA36">
-        <v>0.13765708771521373</v>
+        <v>0.37843436753176884</v>
       </c>
       <c r="BB36">
-        <v>6.4794029709809395E-2</v>
+        <v>0.17169603373048484</v>
       </c>
       <c r="BC36">
-        <v>6.1577238873271746E-2</v>
+        <v>0.15973051020307785</v>
       </c>
       <c r="BD36">
-        <v>9.5862792211029016E-2</v>
+        <v>0.23509819633654777</v>
       </c>
       <c r="BE36">
-        <v>0.13702939295123476</v>
+        <v>0.25672303102177385</v>
       </c>
       <c r="BF36">
-        <v>0.14090796020625895</v>
+        <v>0.26475832540480176</v>
       </c>
       <c r="BG36">
-        <v>0.1421020539860392</v>
+        <v>0.32342379793345505</v>
       </c>
       <c r="BI36" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="BJ36" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK36" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL36">
         <v>0.14361851742774945</v>
@@ -8534,94 +10287,94 @@
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
       </c>
       <c r="D37">
-        <v>0.43710028650552701</v>
+        <v>0.57892190762383655</v>
       </c>
       <c r="E37">
-        <v>0.49762425919713921</v>
+        <v>0.56216904285346725</v>
       </c>
       <c r="F37">
-        <v>0.43944747825221109</v>
+        <v>0.55870245101859362</v>
       </c>
       <c r="G37">
-        <v>0.39788282653379853</v>
+        <v>0.48945563530226327</v>
       </c>
       <c r="H37">
-        <v>0.50341032679566267</v>
+        <v>0.49440816120851466</v>
       </c>
       <c r="I37">
-        <v>0.3897508505717821</v>
+        <v>0.49750342020096566</v>
       </c>
       <c r="J37">
-        <v>0.42448143722604165</v>
+        <v>0.52028533989392423</v>
       </c>
       <c r="K37">
-        <v>0.53003426930683695</v>
+        <v>0.43839216163427236</v>
       </c>
       <c r="L37">
-        <v>0.42301696840791736</v>
+        <v>0.44065900741441466</v>
       </c>
       <c r="M37">
-        <v>0.45958356455880039</v>
+        <v>0.47315479675709554</v>
       </c>
       <c r="N37">
-        <v>0.54533281044808934</v>
+        <v>0.53658903468160213</v>
       </c>
       <c r="O37">
-        <v>0.4709061757207238</v>
+        <v>0.5219669785564951</v>
       </c>
       <c r="AU37" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="AV37">
-        <v>0.20644540140115819</v>
+        <v>0.20369351340667513</v>
       </c>
       <c r="AW37">
-        <v>0.17929802092790206</v>
+        <v>0.19499495486185872</v>
       </c>
       <c r="AX37">
-        <v>0.23806586249735051</v>
+        <v>0.19761383006092689</v>
       </c>
       <c r="AY37">
-        <v>0.23919815525340105</v>
+        <v>0.17473946650348862</v>
       </c>
       <c r="AZ37">
-        <v>0.17079849777188225</v>
+        <v>0.17587255991018572</v>
       </c>
       <c r="BA37">
-        <v>0.23766091778438517</v>
+        <v>0.18834831231650784</v>
       </c>
       <c r="BB37">
-        <v>0.13233878274892358</v>
+        <v>7.530668772631699E-2</v>
       </c>
       <c r="BC37">
-        <v>9.1954001319876869E-2</v>
+        <v>9.0415882556690738E-2</v>
       </c>
       <c r="BD37">
-        <v>0.14858084025987753</v>
+        <v>9.8042378087678766E-2</v>
       </c>
       <c r="BE37">
-        <v>0.20823666600258964</v>
+        <v>0.15106391846804648</v>
       </c>
       <c r="BF37">
-        <v>0.17212599121198527</v>
+        <v>0.15419540507108895</v>
       </c>
       <c r="BG37">
-        <v>0.22706636412460207</v>
+        <v>0.15252987562976719</v>
       </c>
       <c r="BI37" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="BJ37" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK37" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL37">
         <v>0.23919815525340105</v>
@@ -8629,97 +10382,1142 @@
     </row>
     <row r="38" spans="2:64" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
       </c>
       <c r="D38">
-        <v>0.40748907986121824</v>
+        <v>0.57328104245571632</v>
       </c>
       <c r="E38">
-        <v>0.50791726089410238</v>
+        <v>0.56879098077204326</v>
       </c>
       <c r="F38">
-        <v>0.43684343176943147</v>
+        <v>0.57408446194727292</v>
       </c>
       <c r="G38">
-        <v>0.39521632884110519</v>
+        <v>0.55137474583665969</v>
       </c>
       <c r="H38">
-        <v>0.50702747522796543</v>
+        <v>0.52967706923765845</v>
       </c>
       <c r="I38">
-        <v>0.37650920990305564</v>
+        <v>0.53283390336404068</v>
       </c>
       <c r="J38">
-        <v>0.44582278403403636</v>
+        <v>0.55576830981822489</v>
       </c>
       <c r="K38">
-        <v>0.54741379023787096</v>
+        <v>0.48846160326515076</v>
       </c>
       <c r="L38">
-        <v>0.44439590479464947</v>
+        <v>0.4442402467977854</v>
       </c>
       <c r="M38">
-        <v>0.45865505009846252</v>
+        <v>0.53261676360763432</v>
       </c>
       <c r="N38">
-        <v>0.5244046972057782</v>
+        <v>0.55541016763651696</v>
       </c>
       <c r="O38">
-        <v>0.42638835208892806</v>
+        <v>0.52900572458623485</v>
       </c>
       <c r="AU38" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AV38">
-        <v>0.2210869622348236</v>
+        <v>0.2186337042324776</v>
       </c>
       <c r="AW38">
-        <v>0.16565758092479582</v>
+        <v>0.20872767166693784</v>
       </c>
       <c r="AX38">
-        <v>0.22658417150508012</v>
+        <v>0.20835778653156878</v>
       </c>
       <c r="AY38">
-        <v>0.21748280819179441</v>
+        <v>0.19228122880192089</v>
       </c>
       <c r="AZ38">
-        <v>0.16069095608083558</v>
+        <v>0.19973958333187924</v>
       </c>
       <c r="BA38">
-        <v>0.19772533286596566</v>
+        <v>0.20485700014958377</v>
       </c>
       <c r="BB38">
-        <v>0.12375149909941542</v>
+        <v>6.3480275130860131E-2</v>
       </c>
       <c r="BC38">
-        <v>8.3223150422277806E-2</v>
+        <v>8.372217419027371E-2</v>
       </c>
       <c r="BD38">
-        <v>0.13805599208420111</v>
+        <v>0.10317446330459316</v>
       </c>
       <c r="BE38">
-        <v>0.20554226255633085</v>
+        <v>0.19724068420119856</v>
       </c>
       <c r="BF38">
-        <v>0.16661228827983721</v>
+        <v>0.18422254047343278</v>
       </c>
       <c r="BG38">
-        <v>0.21004842897624901</v>
+        <v>0.18883137089035512</v>
       </c>
       <c r="BI38" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="BJ38" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="BK38" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL38">
         <v>0.22658417150508012</v>
+      </c>
+    </row>
+    <row r="39" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39">
+        <v>0.52705410088583815</v>
+      </c>
+      <c r="E39">
+        <v>0.55642496977544753</v>
+      </c>
+      <c r="F39">
+        <v>0.54371133154559348</v>
+      </c>
+      <c r="G39">
+        <v>0.47204817080521755</v>
+      </c>
+      <c r="H39">
+        <v>0.54511938842890284</v>
+      </c>
+      <c r="I39">
+        <v>0.4949264794500049</v>
+      </c>
+      <c r="J39">
+        <v>0.54982485496735034</v>
+      </c>
+      <c r="K39">
+        <v>0.58794929913672922</v>
+      </c>
+      <c r="L39">
+        <v>0.61726975139200624</v>
+      </c>
+      <c r="M39">
+        <v>0.51914580653983899</v>
+      </c>
+      <c r="N39">
+        <v>0.53131062499106452</v>
+      </c>
+      <c r="O39">
+        <v>0.51624643311855101</v>
+      </c>
+      <c r="AU39" t="s">
+        <v>131</v>
+      </c>
+      <c r="AV39">
+        <v>0.26947615458344037</v>
+      </c>
+      <c r="AW39">
+        <v>0.24194009927589816</v>
+      </c>
+      <c r="AX39">
+        <v>0.25023034133264255</v>
+      </c>
+      <c r="AY39">
+        <v>0.23238795446024321</v>
+      </c>
+      <c r="AZ39">
+        <v>0.20106531312443676</v>
+      </c>
+      <c r="BA39">
+        <v>0.22405546674378485</v>
+      </c>
+      <c r="BB39">
+        <v>0.15374964426566418</v>
+      </c>
+      <c r="BC39">
+        <v>0.10351524482199274</v>
+      </c>
+      <c r="BD39">
+        <v>9.9911550324906631E-2</v>
+      </c>
+      <c r="BE39">
+        <v>0.25157142879393224</v>
+      </c>
+      <c r="BF39">
+        <v>0.25758623738923847</v>
+      </c>
+      <c r="BG39">
+        <v>0.26487324156774861</v>
+      </c>
+      <c r="BI39" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ39" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK39" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL39">
+        <v>0.28556891539186685</v>
+      </c>
+    </row>
+    <row r="40" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40">
+        <v>0.53496725529204692</v>
+      </c>
+      <c r="E40">
+        <v>0.54859048834673718</v>
+      </c>
+      <c r="F40">
+        <v>0.5309255994311155</v>
+      </c>
+      <c r="G40">
+        <v>0.51939031581564188</v>
+      </c>
+      <c r="H40">
+        <v>0.52646027747227309</v>
+      </c>
+      <c r="I40">
+        <v>0.5472588150175397</v>
+      </c>
+      <c r="J40">
+        <v>0.5918672556049257</v>
+      </c>
+      <c r="K40">
+        <v>0.54502308404774547</v>
+      </c>
+      <c r="L40">
+        <v>0.64237137992239413</v>
+      </c>
+      <c r="M40">
+        <v>0.54731096377687249</v>
+      </c>
+      <c r="N40">
+        <v>0.53287758101686633</v>
+      </c>
+      <c r="O40">
+        <v>0.54411512439006648</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV40">
+        <v>0.14984587266811897</v>
+      </c>
+      <c r="AW40">
+        <v>0.13602056818009348</v>
+      </c>
+      <c r="AX40">
+        <v>0.14600372150251845</v>
+      </c>
+      <c r="AY40">
+        <v>9.0828534798825064E-2</v>
+      </c>
+      <c r="AZ40">
+        <v>0.10966575677036557</v>
+      </c>
+      <c r="BA40">
+        <v>9.4847115738401155E-2</v>
+      </c>
+      <c r="BB40">
+        <v>5.372129455490162E-2</v>
+      </c>
+      <c r="BC40">
+        <v>7.9911802576982202E-2</v>
+      </c>
+      <c r="BD40">
+        <v>5.1721956758200079E-2</v>
+      </c>
+      <c r="BE40">
+        <v>0.11809070232445909</v>
+      </c>
+      <c r="BF40">
+        <v>0.14092658017829146</v>
+      </c>
+      <c r="BG40">
+        <v>0.11829073459395303</v>
+      </c>
+      <c r="BI40" t="s">
+        <v>119</v>
+      </c>
+      <c r="BJ40" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK40" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL40">
+        <v>0.37991305316373924</v>
+      </c>
+    </row>
+    <row r="41" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41">
+        <v>0.46875530612657806</v>
+      </c>
+      <c r="E41">
+        <v>0.51693528458148885</v>
+      </c>
+      <c r="F41">
+        <v>0.48072250116858939</v>
+      </c>
+      <c r="G41">
+        <v>0.50123349140010887</v>
+      </c>
+      <c r="H41">
+        <v>0.54115582969230014</v>
+      </c>
+      <c r="I41">
+        <v>0.53837280679671495</v>
+      </c>
+      <c r="J41">
+        <v>0.5323633471868966</v>
+      </c>
+      <c r="K41">
+        <v>0.50767143019232697</v>
+      </c>
+      <c r="L41">
+        <v>0.48109271224314643</v>
+      </c>
+      <c r="M41">
+        <v>0.48585808579285983</v>
+      </c>
+      <c r="N41">
+        <v>0.51660760910353021</v>
+      </c>
+      <c r="O41">
+        <v>0.47376573622842516</v>
+      </c>
+      <c r="AU41" t="s">
+        <v>133</v>
+      </c>
+      <c r="AV41">
+        <v>0.28504526951035125</v>
+      </c>
+      <c r="AW41">
+        <v>0.23241706671233073</v>
+      </c>
+      <c r="AX41">
+        <v>0.26541730182654477</v>
+      </c>
+      <c r="AY41">
+        <v>0.19958730917235032</v>
+      </c>
+      <c r="AZ41">
+        <v>0.19835987200837721</v>
+      </c>
+      <c r="BA41">
+        <v>0.17545198604711298</v>
+      </c>
+      <c r="BB41">
+        <v>0.11957950025971902</v>
+      </c>
+      <c r="BC41">
+        <v>0.11724510515813562</v>
+      </c>
+      <c r="BD41">
+        <v>0.12605491550782819</v>
+      </c>
+      <c r="BE41">
+        <v>0.2045797141901097</v>
+      </c>
+      <c r="BF41">
+        <v>0.18280890097467858</v>
+      </c>
+      <c r="BG41">
+        <v>0.2052346236346112</v>
+      </c>
+      <c r="BI41" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ41" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK41" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL41">
+        <v>0.34213719471866261</v>
+      </c>
+    </row>
+    <row r="42" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42">
+        <v>0.54899173912775678</v>
+      </c>
+      <c r="E42">
+        <v>0.56465514685904783</v>
+      </c>
+      <c r="F42">
+        <v>0.55949219755217339</v>
+      </c>
+      <c r="G42">
+        <v>0.57129752125963373</v>
+      </c>
+      <c r="H42">
+        <v>0.60620383024656965</v>
+      </c>
+      <c r="I42">
+        <v>0.60870922265287131</v>
+      </c>
+      <c r="J42">
+        <v>0.63417784407654787</v>
+      </c>
+      <c r="K42">
+        <v>0.58254252491701219</v>
+      </c>
+      <c r="L42">
+        <v>0.60232715098902123</v>
+      </c>
+      <c r="M42">
+        <v>0.55614056152757307</v>
+      </c>
+      <c r="N42">
+        <v>0.5608524853425878</v>
+      </c>
+      <c r="O42">
+        <v>0.53572907378539947</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV42">
+        <v>0.14817382942767271</v>
+      </c>
+      <c r="AW42">
+        <v>0.12961546165317836</v>
+      </c>
+      <c r="AX42">
+        <v>0.133261330786835</v>
+      </c>
+      <c r="AY42">
+        <v>0.11609753306985576</v>
+      </c>
+      <c r="AZ42">
+        <v>0.11979077951729598</v>
+      </c>
+      <c r="BA42">
+        <v>0.11205738127221894</v>
+      </c>
+      <c r="BB42">
+        <v>3.3348814493915198E-2</v>
+      </c>
+      <c r="BC42">
+        <v>5.9832806113654845E-2</v>
+      </c>
+      <c r="BD42">
+        <v>3.7629637330862366E-2</v>
+      </c>
+      <c r="BE42">
+        <v>0.11136928057072905</v>
+      </c>
+      <c r="BF42">
+        <v>0.10582348124556699</v>
+      </c>
+      <c r="BG42">
+        <v>0.11121142306366208</v>
+      </c>
+      <c r="BI42" t="s">
+        <v>121</v>
+      </c>
+      <c r="BJ42" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK42" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL42">
+        <v>0.36452403159933444</v>
+      </c>
+    </row>
+    <row r="43" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43">
+        <v>0.47386780387881305</v>
+      </c>
+      <c r="E43">
+        <v>0.51330726620812894</v>
+      </c>
+      <c r="F43">
+        <v>0.47792483467379276</v>
+      </c>
+      <c r="G43">
+        <v>0.52141007579705168</v>
+      </c>
+      <c r="H43">
+        <v>0.52160449380856155</v>
+      </c>
+      <c r="I43">
+        <v>0.5389018496341037</v>
+      </c>
+      <c r="J43">
+        <v>0.5403754950926476</v>
+      </c>
+      <c r="K43">
+        <v>0.53919002807501759</v>
+      </c>
+      <c r="L43">
+        <v>0.53162483170196762</v>
+      </c>
+      <c r="M43">
+        <v>0.4860408503251244</v>
+      </c>
+      <c r="N43">
+        <v>0.48686830370897549</v>
+      </c>
+      <c r="O43">
+        <v>0.46872525783728464</v>
+      </c>
+      <c r="AU43" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV43">
+        <v>0.16694453608547899</v>
+      </c>
+      <c r="AW43">
+        <v>0.15000189571173506</v>
+      </c>
+      <c r="AX43">
+        <v>0.15258825424762915</v>
+      </c>
+      <c r="AY43">
+        <v>0.12348236416897743</v>
+      </c>
+      <c r="AZ43">
+        <v>0.1584069430929208</v>
+      </c>
+      <c r="BA43">
+        <v>0.12191438118184995</v>
+      </c>
+      <c r="BB43">
+        <v>5.9451421126396474E-2</v>
+      </c>
+      <c r="BC43">
+        <v>0.10796079978461877</v>
+      </c>
+      <c r="BD43">
+        <v>7.1748862572750566E-2</v>
+      </c>
+      <c r="BE43">
+        <v>0.11894229390178822</v>
+      </c>
+      <c r="BF43">
+        <v>0.13287140056803814</v>
+      </c>
+      <c r="BG43">
+        <v>0.11858382003111445</v>
+      </c>
+      <c r="BI43" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ43" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK43" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL43">
+        <v>0.27322828288243717</v>
+      </c>
+    </row>
+    <row r="44" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44">
+        <v>0.48185553843964513</v>
+      </c>
+      <c r="E44">
+        <v>0.56964786342726559</v>
+      </c>
+      <c r="F44">
+        <v>0.44832426131563591</v>
+      </c>
+      <c r="G44">
+        <v>0.47170772428678942</v>
+      </c>
+      <c r="H44">
+        <v>0.55759870443478099</v>
+      </c>
+      <c r="I44">
+        <v>0.40537401206637347</v>
+      </c>
+      <c r="J44">
+        <v>0.4652699180465466</v>
+      </c>
+      <c r="K44">
+        <v>0.55910718442183105</v>
+      </c>
+      <c r="L44">
+        <v>0.41684138098023105</v>
+      </c>
+      <c r="M44">
+        <v>0.47617387723311899</v>
+      </c>
+      <c r="N44">
+        <v>0.56043981496736084</v>
+      </c>
+      <c r="O44">
+        <v>0.43596938013381753</v>
+      </c>
+      <c r="AU44" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV44">
+        <v>0.15876763548459355</v>
+      </c>
+      <c r="AW44">
+        <v>0.10576978818192537</v>
+      </c>
+      <c r="AX44">
+        <v>0.14992170591636053</v>
+      </c>
+      <c r="AY44">
+        <v>0.1321696570218425</v>
+      </c>
+      <c r="AZ44">
+        <v>0.12035742658568196</v>
+      </c>
+      <c r="BA44">
+        <v>0.14379396175678688</v>
+      </c>
+      <c r="BB44">
+        <v>8.527668233543502E-2</v>
+      </c>
+      <c r="BC44">
+        <v>6.0448357068224101E-2</v>
+      </c>
+      <c r="BD44">
+        <v>9.0955994304572491E-2</v>
+      </c>
+      <c r="BE44">
+        <v>0.12235518373597128</v>
+      </c>
+      <c r="BF44">
+        <v>0.10226014148695747</v>
+      </c>
+      <c r="BG44">
+        <v>0.13178530217096121</v>
+      </c>
+      <c r="BI44" t="s">
+        <v>123</v>
+      </c>
+      <c r="BJ44" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK44" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL44">
+        <v>0.31326665298353806</v>
+      </c>
+    </row>
+    <row r="45" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45">
+        <v>0.43889105811303908</v>
+      </c>
+      <c r="E45">
+        <v>0.54996770753102719</v>
+      </c>
+      <c r="F45">
+        <v>0.41499659614663975</v>
+      </c>
+      <c r="G45">
+        <v>0.41699593648517574</v>
+      </c>
+      <c r="H45">
+        <v>0.53205515618654753</v>
+      </c>
+      <c r="I45">
+        <v>0.39549973166085894</v>
+      </c>
+      <c r="J45">
+        <v>0.41817749638207752</v>
+      </c>
+      <c r="K45">
+        <v>0.56679185279610034</v>
+      </c>
+      <c r="L45">
+        <v>0.41511669086440778</v>
+      </c>
+      <c r="M45">
+        <v>0.42973688467532861</v>
+      </c>
+      <c r="N45">
+        <v>0.52460575089762518</v>
+      </c>
+      <c r="O45">
+        <v>0.39199195731259823</v>
+      </c>
+      <c r="AU45" t="s">
+        <v>137</v>
+      </c>
+      <c r="AV45">
+        <v>0.2081188959446553</v>
+      </c>
+      <c r="AW45">
+        <v>0.14455049442503548</v>
+      </c>
+      <c r="AX45">
+        <v>0.21169627590616868</v>
+      </c>
+      <c r="AY45">
+        <v>0.1650032669157942</v>
+      </c>
+      <c r="AZ45">
+        <v>0.13820612539089708</v>
+      </c>
+      <c r="BA45">
+        <v>0.17419706887386943</v>
+      </c>
+      <c r="BB45">
+        <v>0.11548166212981592</v>
+      </c>
+      <c r="BC45">
+        <v>7.0704672104585906E-2</v>
+      </c>
+      <c r="BD45">
+        <v>0.11726975310119528</v>
+      </c>
+      <c r="BE45">
+        <v>0.16996208614188521</v>
+      </c>
+      <c r="BF45">
+        <v>0.13152649001402134</v>
+      </c>
+      <c r="BG45">
+        <v>0.17860347381011976</v>
+      </c>
+      <c r="BI45" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ45" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK45" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL45">
+        <v>0.28371331253019821</v>
+      </c>
+    </row>
+    <row r="46" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46">
+        <v>0.46005603239494119</v>
+      </c>
+      <c r="E46">
+        <v>0.53675089926147979</v>
+      </c>
+      <c r="F46">
+        <v>0.45931862125680684</v>
+      </c>
+      <c r="G46">
+        <v>0.4480715206538039</v>
+      </c>
+      <c r="H46">
+        <v>0.56117120800424969</v>
+      </c>
+      <c r="I46">
+        <v>0.41218917588748211</v>
+      </c>
+      <c r="J46">
+        <v>0.50519506433685613</v>
+      </c>
+      <c r="K46">
+        <v>0.60358158247437199</v>
+      </c>
+      <c r="L46">
+        <v>0.45222485075627655</v>
+      </c>
+      <c r="M46">
+        <v>0.49042295663712754</v>
+      </c>
+      <c r="N46">
+        <v>0.57454003676448273</v>
+      </c>
+      <c r="O46">
+        <v>0.44085219496445044</v>
+      </c>
+      <c r="AU46" t="s">
+        <v>138</v>
+      </c>
+      <c r="AV46">
+        <v>0.14013308658561607</v>
+      </c>
+      <c r="AW46">
+        <v>9.4577599922550923E-2</v>
+      </c>
+      <c r="AX46">
+        <v>0.15062430379992675</v>
+      </c>
+      <c r="AY46">
+        <v>0.13271230088904068</v>
+      </c>
+      <c r="AZ46">
+        <v>9.6179275635501285E-2</v>
+      </c>
+      <c r="BA46">
+        <v>0.13755388150587203</v>
+      </c>
+      <c r="BB46">
+        <v>7.7506812960281501E-2</v>
+      </c>
+      <c r="BC46">
+        <v>5.2168417347353904E-2</v>
+      </c>
+      <c r="BD46">
+        <v>0.10550855423420852</v>
+      </c>
+      <c r="BE46">
+        <v>0.13731834713686256</v>
+      </c>
+      <c r="BF46">
+        <v>0.10430301311530919</v>
+      </c>
+      <c r="BG46">
+        <v>0.14399773360194409</v>
+      </c>
+      <c r="BI46" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ46" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK46" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL46">
+        <v>0.33400297200217077</v>
+      </c>
+    </row>
+    <row r="47" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47">
+        <v>0.52924742569917493</v>
+      </c>
+      <c r="E47">
+        <v>0.58075903976353449</v>
+      </c>
+      <c r="F47">
+        <v>0.53836328139037992</v>
+      </c>
+      <c r="G47">
+        <v>0.52351877866556784</v>
+      </c>
+      <c r="H47">
+        <v>0.57131800339146077</v>
+      </c>
+      <c r="I47">
+        <v>0.46050445061372136</v>
+      </c>
+      <c r="J47">
+        <v>0.61809686081619386</v>
+      </c>
+      <c r="K47">
+        <v>0.59621972436891857</v>
+      </c>
+      <c r="L47">
+        <v>0.50712111620686096</v>
+      </c>
+      <c r="M47">
+        <v>0.54877734650392596</v>
+      </c>
+      <c r="N47">
+        <v>0.59288587818348848</v>
+      </c>
+      <c r="O47">
+        <v>0.52207926199718191</v>
+      </c>
+      <c r="AU47" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV47">
+        <v>0.14013315443927093</v>
+      </c>
+      <c r="AW47">
+        <v>0.11678027147943203</v>
+      </c>
+      <c r="AX47">
+        <v>0.14361851742774945</v>
+      </c>
+      <c r="AY47">
+        <v>0.12768068970596627</v>
+      </c>
+      <c r="AZ47">
+        <v>0.11741801186073036</v>
+      </c>
+      <c r="BA47">
+        <v>0.13765708771521373</v>
+      </c>
+      <c r="BB47">
+        <v>6.4794029709809395E-2</v>
+      </c>
+      <c r="BC47">
+        <v>6.1577238873271746E-2</v>
+      </c>
+      <c r="BD47">
+        <v>9.5862792211029016E-2</v>
+      </c>
+      <c r="BE47">
+        <v>0.13702939295123476</v>
+      </c>
+      <c r="BF47">
+        <v>0.14090796020625895</v>
+      </c>
+      <c r="BG47">
+        <v>0.1421020539860392</v>
+      </c>
+      <c r="BI47" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ47" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK47" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL47">
+        <v>0.31272038286604792</v>
+      </c>
+    </row>
+    <row r="48" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48">
+        <v>0.43710028650552701</v>
+      </c>
+      <c r="E48">
+        <v>0.49762425919713921</v>
+      </c>
+      <c r="F48">
+        <v>0.43944747825221109</v>
+      </c>
+      <c r="G48">
+        <v>0.39788282653379853</v>
+      </c>
+      <c r="H48">
+        <v>0.50341032679566267</v>
+      </c>
+      <c r="I48">
+        <v>0.3897508505717821</v>
+      </c>
+      <c r="J48">
+        <v>0.42448143722604165</v>
+      </c>
+      <c r="K48">
+        <v>0.53003426930683695</v>
+      </c>
+      <c r="L48">
+        <v>0.42301696840791736</v>
+      </c>
+      <c r="M48">
+        <v>0.45958356455880039</v>
+      </c>
+      <c r="N48">
+        <v>0.54533281044808934</v>
+      </c>
+      <c r="O48">
+        <v>0.4709061757207238</v>
+      </c>
+      <c r="AU48" t="s">
+        <v>140</v>
+      </c>
+      <c r="AV48">
+        <v>0.20644540140115819</v>
+      </c>
+      <c r="AW48">
+        <v>0.17929802092790206</v>
+      </c>
+      <c r="AX48">
+        <v>0.23806586249735051</v>
+      </c>
+      <c r="AY48">
+        <v>0.23919815525340105</v>
+      </c>
+      <c r="AZ48">
+        <v>0.17079849777188225</v>
+      </c>
+      <c r="BA48">
+        <v>0.23766091778438517</v>
+      </c>
+      <c r="BB48">
+        <v>0.13233878274892358</v>
+      </c>
+      <c r="BC48">
+        <v>9.1954001319876869E-2</v>
+      </c>
+      <c r="BD48">
+        <v>0.14858084025987753</v>
+      </c>
+      <c r="BE48">
+        <v>0.20823666600258964</v>
+      </c>
+      <c r="BF48">
+        <v>0.17212599121198527</v>
+      </c>
+      <c r="BG48">
+        <v>0.22706636412460207</v>
+      </c>
+      <c r="BI48" t="s">
+        <v>127</v>
+      </c>
+      <c r="BJ48" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK48" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL48">
+        <v>0.3222353285844029</v>
+      </c>
+    </row>
+    <row r="49" spans="2:64" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49">
+        <v>0.40748907986121824</v>
+      </c>
+      <c r="E49">
+        <v>0.50791726089410238</v>
+      </c>
+      <c r="F49">
+        <v>0.43684343176943147</v>
+      </c>
+      <c r="G49">
+        <v>0.39521632884110519</v>
+      </c>
+      <c r="H49">
+        <v>0.50702747522796543</v>
+      </c>
+      <c r="I49">
+        <v>0.37650920990305564</v>
+      </c>
+      <c r="J49">
+        <v>0.44582278403403636</v>
+      </c>
+      <c r="K49">
+        <v>0.54741379023787096</v>
+      </c>
+      <c r="L49">
+        <v>0.44439590479464947</v>
+      </c>
+      <c r="M49">
+        <v>0.45865505009846252</v>
+      </c>
+      <c r="N49">
+        <v>0.5244046972057782</v>
+      </c>
+      <c r="O49">
+        <v>0.42638835208892806</v>
+      </c>
+      <c r="AU49" t="s">
+        <v>141</v>
+      </c>
+      <c r="AV49">
+        <v>0.2210869622348236</v>
+      </c>
+      <c r="AW49">
+        <v>0.16565758092479582</v>
+      </c>
+      <c r="AX49">
+        <v>0.22658417150508012</v>
+      </c>
+      <c r="AY49">
+        <v>0.21748280819179441</v>
+      </c>
+      <c r="AZ49">
+        <v>0.16069095608083558</v>
+      </c>
+      <c r="BA49">
+        <v>0.19772533286596566</v>
+      </c>
+      <c r="BB49">
+        <v>0.12375149909941542</v>
+      </c>
+      <c r="BC49">
+        <v>8.3223150422277806E-2</v>
+      </c>
+      <c r="BD49">
+        <v>0.13805599208420111</v>
+      </c>
+      <c r="BE49">
+        <v>0.20554226255633085</v>
+      </c>
+      <c r="BF49">
+        <v>0.16661228827983721</v>
+      </c>
+      <c r="BG49">
+        <v>0.21004842897624901</v>
+      </c>
+      <c r="BI49" t="s">
+        <v>128</v>
+      </c>
+      <c r="BJ49" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK49" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL49">
+        <v>0.37843436753176884</v>
       </c>
     </row>
   </sheetData>
@@ -8728,7 +11526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC67565-769A-4A63-B370-07B442CC7523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1E4564-78F4-4130-9734-B96E351D88F6}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8755,7 +11553,7 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
         <v>49</v>
@@ -8782,19 +11580,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="S10" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -8812,10 +11610,10 @@
         <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H11" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -8839,7 +11637,7 @@
         <v>0.34706666666666663</v>
       </c>
       <c r="S11" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -8853,10 +11651,10 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -8880,7 +11678,7 @@
         <v>0.20766666666666667</v>
       </c>
       <c r="S12" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -8894,10 +11692,10 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H13" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -8918,10 +11716,10 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.17110000000000003</v>
+        <v>0.1711</v>
       </c>
       <c r="S13" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -8935,10 +11733,10 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -8962,7 +11760,7 @@
         <v>0.26543333333333335</v>
       </c>
       <c r="S14" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -8976,10 +11774,10 @@
         <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -9003,7 +11801,7 @@
         <v>0.51186666666666669</v>
       </c>
       <c r="S15" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -9017,10 +11815,10 @@
         <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H16" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -9044,7 +11842,7 @@
         <v>0.37233333333333335</v>
       </c>
       <c r="S16" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -9058,10 +11856,10 @@
         <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -9082,10 +11880,10 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S17" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -9099,10 +11897,10 @@
         <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H18" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -9126,7 +11924,7 @@
         <v>0.18783333333333332</v>
       </c>
       <c r="S18" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -9140,10 +11938,10 @@
         <v>61</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -9167,7 +11965,7 @@
         <v>0.36303333333333332</v>
       </c>
       <c r="S19" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -9181,10 +11979,10 @@
         <v>62</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -9208,7 +12006,7 @@
         <v>0.21736666666666668</v>
       </c>
       <c r="S20" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -9222,10 +12020,10 @@
         <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -9249,7 +12047,7 @@
         <v>0.16026666666666667</v>
       </c>
       <c r="S21" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -9263,10 +12061,10 @@
         <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="H22" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -9287,15 +12085,15 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.18273333333333333</v>
+        <v>0.1827333333333333</v>
       </c>
       <c r="S22" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -9310,12 +12108,12 @@
         <v>0.43609999999999999</v>
       </c>
       <c r="S23" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -9330,12 +12128,12 @@
         <v>0.31580000000000003</v>
       </c>
       <c r="S24" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -9350,12 +12148,12 @@
         <v>0.26203333333333334</v>
       </c>
       <c r="S25" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -9370,12 +12168,12 @@
         <v>0.27509999999999996</v>
       </c>
       <c r="S26" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -9390,12 +12188,12 @@
         <v>0.48209999999999997</v>
       </c>
       <c r="S27" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -9410,12 +12208,12 @@
         <v>0.4289</v>
       </c>
       <c r="S28" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -9430,12 +12228,12 @@
         <v>0.25643333333333335</v>
       </c>
       <c r="S29" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -9447,15 +12245,15 @@
         <v>45</v>
       </c>
       <c r="R30">
-        <v>0.28333333333333333</v>
+        <v>0.28333333333333327</v>
       </c>
       <c r="S30" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -9470,12 +12268,12 @@
         <v>0.38813333333333339</v>
       </c>
       <c r="S31" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -9490,12 +12288,12 @@
         <v>0.36286666666666667</v>
       </c>
       <c r="S32" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -9510,12 +12308,12 @@
         <v>0.26993333333333336</v>
       </c>
       <c r="S33" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -9530,7 +12328,7 @@
         <v>0.24476666666666666</v>
       </c>
       <c r="S34" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -9544,7 +12342,7 @@
         <v>0.4551</v>
       </c>
       <c r="S35" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -9558,7 +12356,7 @@
         <v>0.29773333333333335</v>
       </c>
       <c r="S36" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -9569,10 +12367,10 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.27506666666666663</v>
+        <v>0.27506666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -9586,7 +12384,7 @@
         <v>0.25643333333333335</v>
       </c>
       <c r="S38" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -9597,10 +12395,10 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.48360000000000003</v>
+        <v>0.48359999999999997</v>
       </c>
       <c r="S39" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -9614,7 +12412,7 @@
         <v>0.39773333333333333</v>
       </c>
       <c r="S40" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -9628,7 +12426,7 @@
         <v>0.25569999999999998</v>
       </c>
       <c r="S41" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -9642,7 +12440,7 @@
         <v>0.28470000000000001</v>
       </c>
       <c r="S42" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -9656,7 +12454,7 @@
         <v>0.53743333333333332</v>
       </c>
       <c r="S43" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -9670,7 +12468,7 @@
         <v>0.37093333333333334</v>
       </c>
       <c r="S44" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -9684,7 +12482,7 @@
         <v>0.31076666666666669</v>
       </c>
       <c r="S45" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -9698,7 +12496,7 @@
         <v>0.32246666666666668</v>
       </c>
       <c r="S46" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -9712,7 +12510,7 @@
         <v>0.43563333333333332</v>
       </c>
       <c r="S47" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -9726,7 +12524,7 @@
         <v>0.37220000000000003</v>
       </c>
       <c r="S48" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -9740,7 +12538,7 @@
         <v>0.29293333333333332</v>
       </c>
       <c r="S49" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -9754,7 +12552,7 @@
         <v>0.25473333333333331</v>
       </c>
       <c r="S50" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -9768,7 +12566,7 @@
         <v>0.49980000000000002</v>
       </c>
       <c r="S51" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -9782,7 +12580,7 @@
         <v>0.38233333333333336</v>
       </c>
       <c r="S52" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -9796,7 +12594,7 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="S53" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -9807,10 +12605,10 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22869999999999999</v>
+        <v>0.22870000000000001</v>
       </c>
       <c r="S54" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -9824,7 +12622,7 @@
         <v>0.5033333333333333</v>
       </c>
       <c r="S55" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -9838,7 +12636,7 @@
         <v>0.39116666666666666</v>
       </c>
       <c r="S56" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -9852,7 +12650,7 @@
         <v>0.24456666666666668</v>
       </c>
       <c r="S57" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -9866,7 +12664,7 @@
         <v>0.27540000000000003</v>
       </c>
       <c r="S58" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -9877,10 +12675,10 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.56483333333333341</v>
+        <v>0.5648333333333333</v>
       </c>
       <c r="S59" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -9894,7 +12692,7 @@
         <v>0.2775333333333333</v>
       </c>
       <c r="S60" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -9908,7 +12706,7 @@
         <v>0.32469999999999999</v>
       </c>
       <c r="S61" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -9922,7 +12720,7 @@
         <v>0.34383333333333327</v>
       </c>
       <c r="S62" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -9936,7 +12734,7 @@
         <v>0.49216666666666664</v>
       </c>
       <c r="S63" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -9950,7 +12748,7 @@
         <v>0.39883333333333332</v>
       </c>
       <c r="S64" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -9961,10 +12759,10 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.32963333333333333</v>
+        <v>0.32963333333333328</v>
       </c>
       <c r="S65" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -9978,7 +12776,7 @@
         <v>0.28689999999999999</v>
       </c>
       <c r="S66" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -9989,10 +12787,10 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.49983333333333335</v>
+        <v>0.4998333333333333</v>
       </c>
       <c r="S67" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -10006,7 +12804,7 @@
         <v>0.375</v>
       </c>
       <c r="S68" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -10020,7 +12818,7 @@
         <v>0.23596666666666666</v>
       </c>
       <c r="S69" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -10034,7 +12832,7 @@
         <v>0.25093333333333329</v>
       </c>
       <c r="S70" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -10048,7 +12846,7 @@
         <v>0.45046666666666663</v>
       </c>
       <c r="S71" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -10062,7 +12860,7 @@
         <v>0.39326666666666665</v>
       </c>
       <c r="S72" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -10076,7 +12874,7 @@
         <v>0.18996666666666664</v>
       </c>
       <c r="S73" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -10090,7 +12888,7 @@
         <v>0.19753333333333334</v>
       </c>
       <c r="S74" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -10104,7 +12902,7 @@
         <v>0.46633333333333332</v>
       </c>
       <c r="S75" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -10118,7 +12916,7 @@
         <v>0.35016666666666668</v>
       </c>
       <c r="S76" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -10129,10 +12927,10 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.29143333333333338</v>
+        <v>0.29143333333333332</v>
       </c>
       <c r="S77" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -10146,7 +12944,7 @@
         <v>0.29396666666666665</v>
       </c>
       <c r="S78" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -10157,10 +12955,10 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.4746333333333333</v>
+        <v>0.47463333333333341</v>
       </c>
       <c r="S79" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -10174,7 +12972,7 @@
         <v>0.30596666666666666</v>
       </c>
       <c r="S80" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -10185,10 +12983,10 @@
         <v>43</v>
       </c>
       <c r="R81">
-        <v>0.30869999999999997</v>
+        <v>0.30870000000000003</v>
       </c>
       <c r="S81" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -10202,7 +13000,7 @@
         <v>0.3231</v>
       </c>
       <c r="S82" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -10213,10 +13011,10 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.50239999999999996</v>
+        <v>0.50240000000000007</v>
       </c>
       <c r="S83" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -10230,7 +13028,7 @@
         <v>0.44913333333333333</v>
       </c>
       <c r="S84" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -10244,7 +13042,7 @@
         <v>0.25846666666666668</v>
       </c>
       <c r="S85" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -10258,7 +13056,7 @@
         <v>0.29776666666666668</v>
       </c>
       <c r="S86" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -10272,7 +13070,7 @@
         <v>0.51239999999999997</v>
       </c>
       <c r="S87" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -10286,7 +13084,7 @@
         <v>0.40939999999999999</v>
       </c>
       <c r="S88" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -10300,7 +13098,7 @@
         <v>0.32106666666666667</v>
       </c>
       <c r="S89" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -10314,7 +13112,7 @@
         <v>0.2525</v>
       </c>
       <c r="S90" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -10328,7 +13126,7 @@
         <v>0.55559999999999998</v>
       </c>
       <c r="S91" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -10342,7 +13140,7 @@
         <v>0.34600000000000003</v>
       </c>
       <c r="S92" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -10356,7 +13154,7 @@
         <v>0.23566666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -10370,7 +13168,7 @@
         <v>0.30580000000000002</v>
       </c>
       <c r="S94" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -10384,7 +13182,7 @@
         <v>0.49429999999999996</v>
       </c>
       <c r="S95" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -10398,7 +13196,7 @@
         <v>0.35983333333333328</v>
       </c>
       <c r="S96" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -10409,10 +13207,10 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="S97" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -10426,7 +13224,7 @@
         <v>0.23119999999999999</v>
       </c>
       <c r="S98" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -10440,7 +13238,7 @@
         <v>0.59</v>
       </c>
       <c r="S99" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -10454,7 +13252,7 @@
         <v>0.32046666666666668</v>
       </c>
       <c r="S100" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -10468,7 +13266,7 @@
         <v>0.32406666666666667</v>
       </c>
       <c r="S101" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -10482,7 +13280,7 @@
         <v>0.31086666666666668</v>
       </c>
       <c r="S102" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -10496,7 +13294,7 @@
         <v>0.44743333333333329</v>
       </c>
       <c r="S103" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -10510,7 +13308,7 @@
         <v>0.45293333333333335</v>
       </c>
       <c r="S104" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -10524,7 +13322,7 @@
         <v>0.30783333333333335</v>
       </c>
       <c r="S105" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -10538,7 +13336,7 @@
         <v>0.23606666666666667</v>
       </c>
       <c r="S106" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -10552,7 +13350,7 @@
         <v>0.46906666666666669</v>
       </c>
       <c r="S107" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -10566,7 +13364,7 @@
         <v>0.34603333333333336</v>
       </c>
       <c r="S108" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -10580,7 +13378,7 @@
         <v>0.3427</v>
       </c>
       <c r="S109" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -10591,10 +13389,10 @@
         <v>45</v>
       </c>
       <c r="R110">
-        <v>0.29020000000000001</v>
+        <v>0.29019999999999996</v>
       </c>
       <c r="S110" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -10608,7 +13406,7 @@
         <v>0.38350000000000001</v>
       </c>
       <c r="S111" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -10622,7 +13420,7 @@
         <v>0.31126666666666664</v>
       </c>
       <c r="S112" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -10636,7 +13434,7 @@
         <v>0.35099999999999998</v>
       </c>
       <c r="S113" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -10650,7 +13448,7 @@
         <v>0.41733333333333333</v>
       </c>
       <c r="S114" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -10661,10 +13459,10 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.54879999999999995</v>
+        <v>0.54880000000000007</v>
       </c>
       <c r="S115" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -10678,7 +13476,7 @@
         <v>0.43486666666666668</v>
       </c>
       <c r="S116" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -10692,7 +13490,7 @@
         <v>0.23729999999999998</v>
       </c>
       <c r="S117" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -10706,7 +13504,7 @@
         <v>0.29993333333333333</v>
       </c>
       <c r="S118" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -10720,7 +13518,7 @@
         <v>0.47163333333333335</v>
       </c>
       <c r="S119" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -10734,7 +13532,7 @@
         <v>0.41349999999999998</v>
       </c>
       <c r="S120" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -10748,7 +13546,7 @@
         <v>0.37373333333333331</v>
       </c>
       <c r="S121" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -10762,7 +13560,7 @@
         <v>0.24793333333333334</v>
       </c>
       <c r="S122" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -10776,7 +13574,7 @@
         <v>0.43120000000000003</v>
       </c>
       <c r="S123" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -10790,7 +13588,7 @@
         <v>0.39643333333333336</v>
       </c>
       <c r="S124" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -10801,10 +13599,10 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.21666666666666667</v>
+        <v>0.21666666666666665</v>
       </c>
       <c r="S125" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -10818,7 +13616,7 @@
         <v>0.23783333333333334</v>
       </c>
       <c r="S126" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D56CCB6-CAA7-47A8-B9FD-3C7B6DB5441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51EE85C7-F586-4772-90B1-F031DA370F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,13 +507,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
+    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3</t>
+    <t>S2aH1,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S1aH3,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3</v>
+        <v>S2aH1,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S1aH3,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
+        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1236,7 +1236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4C679C-EBD1-4ED1-ACF7-4EFD7815812B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97512F2F-734B-4318-936E-1729E6093105}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1320,7 +1320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22546ECA-1805-4E6F-AF6C-898AEC3DE9E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCA4753-9FDB-4175-B446-1EB2B6D8D2FA}">
   <dimension ref="B9:O190"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7358,7 +7358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69A62DD-531B-47E4-9840-BA94A2B12359}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E68CBC8-7AD3-4DEB-9C7E-D5DC087A3641}">
   <dimension ref="B9:BL49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11526,7 +11526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1E4564-78F4-4130-9734-B96E351D88F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0231FAAE-3379-4130-BD01-34321EF86D20}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11716,7 +11716,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.1711</v>
+        <v>0.17110000000000003</v>
       </c>
       <c r="S13" t="s">
         <v>164</v>
@@ -11880,7 +11880,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S17" t="s">
         <v>164</v>
@@ -12044,7 +12044,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.16026666666666667</v>
+        <v>0.16026666666666664</v>
       </c>
       <c r="S21" t="s">
         <v>164</v>
@@ -12305,7 +12305,7 @@
         <v>43</v>
       </c>
       <c r="R33">
-        <v>0.26993333333333336</v>
+        <v>0.2699333333333333</v>
       </c>
       <c r="S33" t="s">
         <v>164</v>
@@ -12367,7 +12367,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.27506666666666668</v>
+        <v>0.27506666666666663</v>
       </c>
       <c r="S37" t="s">
         <v>164</v>
@@ -12927,7 +12927,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.29143333333333332</v>
+        <v>0.29143333333333327</v>
       </c>
       <c r="S77" t="s">
         <v>164</v>
@@ -12983,7 +12983,7 @@
         <v>43</v>
       </c>
       <c r="R81">
-        <v>0.30870000000000003</v>
+        <v>0.30869999999999997</v>
       </c>
       <c r="S81" t="s">
         <v>164</v>
@@ -13151,7 +13151,7 @@
         <v>43</v>
       </c>
       <c r="R93">
-        <v>0.23566666666666669</v>
+        <v>0.23566666666666666</v>
       </c>
       <c r="S93" t="s">
         <v>164</v>
@@ -13207,7 +13207,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.31743333333333335</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="S97" t="s">
         <v>164</v>
@@ -13599,7 +13599,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.21666666666666665</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="S125" t="s">
         <v>164</v>
